--- a/조사1.xlsx
+++ b/조사1.xlsx
@@ -5,24 +5,25 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\프로젝트\조사위치표시\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12170"/>
   </bookViews>
   <sheets>
-    <sheet name="선택된 충전소" sheetId="1" r:id="rId1"/>
+    <sheet name="1차조사" sheetId="2" r:id="rId1"/>
+    <sheet name="선택된 충전소" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'선택된 충전소'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'선택된 충전소'!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10463" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10900" uniqueCount="904">
   <si>
     <t>운영기관</t>
   </si>
@@ -1766,13 +1767,1001 @@
   <si>
     <t>통합본</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시설명</t>
+  </si>
+  <si>
+    <t>광주시립정신병원</t>
+  </si>
+  <si>
+    <t>주차장(전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>옥동 차량기지</t>
+  </si>
+  <si>
+    <t>정문옆(전용2, 급속2)</t>
+  </si>
+  <si>
+    <t>평동화물차고지</t>
+  </si>
+  <si>
+    <t>관리동앞 주차장(전용2, 급속2)</t>
+  </si>
+  <si>
+    <t>국립야생동물질병관리원</t>
+  </si>
+  <si>
+    <t>청사주차장(전용1, 급속1, 완속1)</t>
+  </si>
+  <si>
+    <t>친환경자동차 부품클러스터</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스동 주차장(전용3, 급속2), 기술지원동 주차장(전용1, 급속2)</t>
+  </si>
+  <si>
+    <t>광주친환경자동차인증센터(친환경자동차부품인증센터)</t>
+  </si>
+  <si>
+    <t>주차장(급속1)</t>
+  </si>
+  <si>
+    <t>농업기술센터</t>
+  </si>
+  <si>
+    <t>본관 뒷편 주차장(전용1, 완속1), 제1주차장(전용4, 완속4)</t>
+  </si>
+  <si>
+    <t>송정역 한국아델리움 더 씨티</t>
+  </si>
+  <si>
+    <t>지하 (전용2 충전2) A104구역, 지하 (전용1 충전1) B106구역 (급속)</t>
+  </si>
+  <si>
+    <t>케이티송정빌딩</t>
+  </si>
+  <si>
+    <t>지상 2대</t>
+  </si>
+  <si>
+    <t>SK텔레콤 송정사옥</t>
+  </si>
+  <si>
+    <t>지상 1대</t>
+  </si>
+  <si>
+    <t>효정요양병원</t>
+  </si>
+  <si>
+    <t>신관뒤 주차장(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>광산엘리체 레이크시티</t>
+  </si>
+  <si>
+    <t>102동 뒷편(전용11, 완속11), 104동 앞(전용5, 급속1, 완속4)</t>
+  </si>
+  <si>
+    <t>송정서초등학교</t>
+  </si>
+  <si>
+    <t>지상 1대 완속</t>
+  </si>
+  <si>
+    <t>송정중학교</t>
+  </si>
+  <si>
+    <t>지상 운동장옆 1대</t>
+  </si>
+  <si>
+    <t>광주소프트웨어마이스터고등학교</t>
+  </si>
+  <si>
+    <t>학교 주차장 입구쪽 1대</t>
+  </si>
+  <si>
+    <t>빛그린산학융합캠퍼스</t>
+  </si>
+  <si>
+    <t>연구관 앞 주차장(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>송정금강아파트</t>
+  </si>
+  <si>
+    <t>관리사무소 옆(전용7/충전7), 지하주차장 우측끝(전용2/충전2)</t>
+  </si>
+  <si>
+    <t>송정우방아이유쉘</t>
+  </si>
+  <si>
+    <t>204동 앞 1-2라인 앞(전용6, 완속6), 210동 앞 3-4라인 앞(전용9, 완속9)</t>
+  </si>
+  <si>
+    <t>대화아파트</t>
+  </si>
+  <si>
+    <t>103동 후면 : 전용5/충전5</t>
+  </si>
+  <si>
+    <t>송정역숲안애2차</t>
+  </si>
+  <si>
+    <t>201동앞: 전용4/충전4</t>
+  </si>
+  <si>
+    <t>광산엘리체레이크시티오피스텔</t>
+  </si>
+  <si>
+    <t>104동 앞 : 전용5/충전5 (급속1, 완속4), 102동 앞 : 전용11/충전11</t>
+  </si>
+  <si>
+    <t>도산호반1차</t>
+  </si>
+  <si>
+    <t>101동 옆 후문(전용5, 완속5)</t>
+  </si>
+  <si>
+    <t>도산 우미</t>
+  </si>
+  <si>
+    <t>102동 뒷편(전용4, 병행2, 완속6)</t>
+  </si>
+  <si>
+    <t>도산호반2차</t>
+  </si>
+  <si>
+    <t>203동 5-6라인앞(전용3, 병행4, 완속7), 203동 7-8라인앞(병행3, 완속3)</t>
+  </si>
+  <si>
+    <t>온세계아파트</t>
+  </si>
+  <si>
+    <t>104동 앞 : 전용4/충전4, 지하2주차장:전용5/충전5, 102동 앞 : 전용8/충전8</t>
+  </si>
+  <si>
+    <t>명지 2차&lt;송정명지2차&gt;</t>
+  </si>
+  <si>
+    <t>201동앞 지상1층 전용5/충전5, 206동앞 지상1층 전용4/충전4</t>
+  </si>
+  <si>
+    <t>도산 우방아이유쉘</t>
+  </si>
+  <si>
+    <t>104동 3-4라인 앞(전용4, 완속4), 107동 1-2라인 앞(전용5, 완속5)</t>
+  </si>
+  <si>
+    <t>송정역 모아엘가</t>
+  </si>
+  <si>
+    <t>① 지상 (전용3 충전3) 106동 앞 (병행2), ② 지상 (전용3 충전3) 107동 앞 (병행2), ③ 지상 (전용3 충전3) 104동 앞 (병행2), ④ 지상 (전용6 충전6) 102동 뒤 (병행4), ⑤ 지상 (전용3 충전3) 101동 앞 (병행2), ⑥ 지하 (전용2 충전2) 101동 12라인 앞, ⑦ 지하 (전용1 충전1) 101동 12라인 앞</t>
+  </si>
+  <si>
+    <t>상아</t>
+  </si>
+  <si>
+    <t>지상(전용3 충전3) 101동 앞</t>
+  </si>
+  <si>
+    <t>호반청암빌라트</t>
+  </si>
+  <si>
+    <t>무등파크</t>
+  </si>
+  <si>
+    <t>지하주차장 53-54구역(전용1, 병행1, 완속2)</t>
+  </si>
+  <si>
+    <t>삼라미주</t>
+  </si>
+  <si>
+    <t>지상 주차장 전용5, 충전2</t>
+  </si>
+  <si>
+    <t>대덕9차</t>
+  </si>
+  <si>
+    <t>901동 후면 : 전용7/충전7</t>
+  </si>
+  <si>
+    <t>송정라인1차</t>
+  </si>
+  <si>
+    <t>정문경비실 입구 : 전용5/충전5</t>
+  </si>
+  <si>
+    <t>카이스트빌1</t>
+  </si>
+  <si>
+    <t>지상1층 주차장 전용9/충전4</t>
+  </si>
+  <si>
+    <t>카이스트빌2</t>
+  </si>
+  <si>
+    <t>201동 3-4라인앞(전용2, 병행1, 완속3), 202동 1-2라인앞(전용1, 병행1, 완속2)</t>
+  </si>
+  <si>
+    <t>도산대주2차</t>
+  </si>
+  <si>
+    <t>201동 3-5라인 앞(전용3, 병행1, 완속4)</t>
+  </si>
+  <si>
+    <t>금강2차</t>
+  </si>
+  <si>
+    <t>지상1층 주차장 전용7/충전3</t>
+  </si>
+  <si>
+    <t>해피드림</t>
+  </si>
+  <si>
+    <t>101동 앞 (전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>명지</t>
+  </si>
+  <si>
+    <t>102동 앞: 전용4/충전4</t>
+  </si>
+  <si>
+    <t>신한화</t>
+  </si>
+  <si>
+    <t>지상1층 주차장 전용2/충전2</t>
+  </si>
+  <si>
+    <t>삼라극동</t>
+  </si>
+  <si>
+    <t>서경</t>
+  </si>
+  <si>
+    <t>101동 1-2라인 뒷편(전용2, 병행1, 완속3), 102동 10-11라인 앞(전용1, 병행1, 완속2)</t>
+  </si>
+  <si>
+    <t>극동마이다스</t>
+  </si>
+  <si>
+    <t>지상 (전용 3 충전 3) 아파트입구</t>
+  </si>
+  <si>
+    <t>광신프로그레스</t>
+  </si>
+  <si>
+    <t>지상 (전용 4 충전 4) 102동앞, 지하 (전용 2 충전 2) 101동 (병행2), 지하 (전용 2 충전 2) 102동 (병행2)</t>
+  </si>
+  <si>
+    <t>송정매일시장 주차타워</t>
+  </si>
+  <si>
+    <t>지상3층 A지역: 전용1/충전1(급1), 지상3층 B지역: 전용3/충전3(급3)</t>
+  </si>
+  <si>
+    <t>1913송정역시장 주차타워</t>
+  </si>
+  <si>
+    <t>1층 좌측 : 전용 1, 2층 중앙 : 전용 1, 2층 좌측 : 전용 2 / 충전2, 3층 중앙 : 전용 1, 4층 중앙 : 전용 1</t>
+  </si>
+  <si>
+    <t>송정5일시장 공영주차장</t>
+  </si>
+  <si>
+    <t>지상1층 : 전용8 / 충전4 (급4)</t>
+  </si>
+  <si>
+    <t>광산CC 주차장</t>
+  </si>
+  <si>
+    <t>출입구 좌측 : 전용2/충전2(급2)</t>
+  </si>
+  <si>
+    <t>광산로 제2공영주차장</t>
+  </si>
+  <si>
+    <t>주차장 맨끝: 전용4, 주차장 출구 우측: 전용1 / 충전1 (급1), 주차장 출구 좌측: 전용2 / 충전2 (급2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">광주송정역뒤 공영주차장 </t>
+  </si>
+  <si>
+    <t>출입구 좌측: 전용3/충전1(급1)</t>
+  </si>
+  <si>
+    <t>광산구청사 주차장</t>
+  </si>
+  <si>
+    <t>지하1층 D-7 구역: 전용4 / 충전1(급속), 지하2층 A-6 구역: 전용2 / 충전2(완속)</t>
+  </si>
+  <si>
+    <t>차고지(광산구생활환경종합센터)</t>
+  </si>
+  <si>
+    <t>한국도로교통공단 광주교통방송</t>
+  </si>
+  <si>
+    <t>주차장 (전용2, 급속2), (전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>광주국토관리사무소</t>
+  </si>
+  <si>
+    <t>정문 옆(차고동)(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>광주우편집중국</t>
+  </si>
+  <si>
+    <t>지상1층 전용10/충전4 (급속1, 완속3)</t>
+  </si>
+  <si>
+    <t>보이저 첨단</t>
+  </si>
+  <si>
+    <t>4층 엘리베이터 앞쪽(전용2, 급속2), 6층 테슬라 전용(전용6, 급속6)</t>
+  </si>
+  <si>
+    <t>첨단트레비엔 H-CITY</t>
+  </si>
+  <si>
+    <t>지하2층 03구역(전용1, 급속1(2)), 04구역(전용1, 급속1(3)), 지하2층 상가엘리베이터 입구(전용1, 급속1(3))</t>
+  </si>
+  <si>
+    <t>CMC TOWER&lt;신축유의!&gt;</t>
+  </si>
+  <si>
+    <t>지상4층 A구역(전용4, 완속4), B구역(전용3, 완속3), 지상3층 A구역(전용1, 급속1), B구역(전용4, 완속4), 지상2층 A구역(전용2, 완속2), C구역(전용3, 완속3), 지상2층 B구역(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>야스텍타워</t>
+  </si>
+  <si>
+    <t>지하1층 엘리베이터 앞(전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>쌍암힐스테이트리버파크(오피스텔)</t>
+  </si>
+  <si>
+    <t>지하1층 J09구역(전용2, 완속2), 지하2층 J09구역(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">더 시너지 첨단 </t>
+  </si>
+  <si>
+    <t>지하2층 엘리베이터 앞(전용3, 급속1, 완속2)</t>
+  </si>
+  <si>
+    <t>아크레타 첨단</t>
+  </si>
+  <si>
+    <t>씨네파크(키넥스9시네마)</t>
+  </si>
+  <si>
+    <t>쌍암동 미르채 리버파크 오피스텔</t>
+  </si>
+  <si>
+    <t>지하2층 출구쪽(전용2, 급속1, 완속1), 지하3층 출구쪽(전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>첨단 뉴타운 한국아델리움</t>
+  </si>
+  <si>
+    <t>지하1층 2대 (전용2/충전2) 급속1 완속1, 지하2층 1대 (전용1/충전1)</t>
+  </si>
+  <si>
+    <t>첨단 한국아델리움 메트로시티</t>
+  </si>
+  <si>
+    <t>지하4층 1대 (전용1/충전1)급속, 지하3층 1대 (전용1/충전1), 지하2층 1대 (전용1/충전1)</t>
+  </si>
+  <si>
+    <t>첨단센츄럴빌딩</t>
+  </si>
+  <si>
+    <t>지상4층 주차장(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>첨단중해마루힐 주차타워</t>
+  </si>
+  <si>
+    <t>월계동 주차빌딩(광주첨단점 아이파킹주차장)</t>
+  </si>
+  <si>
+    <t>센트럴파크 첨단주차장</t>
+  </si>
+  <si>
+    <t>힐스테이트 첨단 힐스에비뉴</t>
+  </si>
+  <si>
+    <t>지하1층01구역(전용1, 급속1), 지하1층02구역(전용5, 완속5)</t>
+  </si>
+  <si>
+    <t>첨단 LC타워</t>
+  </si>
+  <si>
+    <t>지하주차장(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>대상파크타운</t>
+  </si>
+  <si>
+    <t>지하주차장 출구쪽(전용4, 완속4)</t>
+  </si>
+  <si>
+    <t>폭스존(메가박스 첨단 건물)</t>
+  </si>
+  <si>
+    <t>쌍암동 첨단프라자</t>
+  </si>
+  <si>
+    <t>지하1층(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>애플타워</t>
+  </si>
+  <si>
+    <t>롯데마트 첨단점</t>
+  </si>
+  <si>
+    <t>주차장 2층 A(전용3, 급속1(3개)), 주차장 2층 B(전용8, 완속6(8개)), 주차장 2층 C(전용1, 급속2(4개))</t>
+  </si>
+  <si>
+    <t>KT 첨단빌딩</t>
+  </si>
+  <si>
+    <t>지상1층 고객주차장(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>광주노블스테이호텔</t>
+  </si>
+  <si>
+    <t>지상1층 출구쪽(전용1, 완속1)</t>
+  </si>
+  <si>
+    <t>cgv 주차타워</t>
+  </si>
+  <si>
+    <t>첨단종합병원</t>
+  </si>
+  <si>
+    <t>원내주차장 1층(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>광주보훈병원</t>
+  </si>
+  <si>
+    <t>요양병원옆 체육관옆(전용6, 완속6), 고객주차장(전용12, 급속2, 완속10), 전용주차구역 1. 주차타워옥상(9) 2. 요양병원앞(4) 3. 장례식장(3) 4. 직원주차장(10)</t>
+  </si>
+  <si>
+    <t>골드타워</t>
+  </si>
+  <si>
+    <t>겨자씨교회</t>
+  </si>
+  <si>
+    <t>다담식자재마트</t>
+  </si>
+  <si>
+    <t>지상4층 4A구역(전용4, 급속1, 완속3)</t>
+  </si>
+  <si>
+    <t>첨단부영3차</t>
+  </si>
+  <si>
+    <t>관리동앞 3대 (지상), 302동앞 3대 (지상), 304동앞 3대 (지상), 305동앞 3대 (지상)</t>
+  </si>
+  <si>
+    <t>쌍암힐스테이트리버파크</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;지하1층&gt;101동 E07 2대, 102동 C19 2대, 105동 V09 2대 &lt;지하2층&gt;105동 T12 3대, 105동 T10 2대, 105동 T09 1대, 101동 E13 2대, D13 2대, 101동 C13·14·15 콘센트형 3대, 101동 B2 2대, 102동 C21 2대, 105동 O12 콘센트형 2대 &lt;지하3층&gt;109동 B3 2대, 109동 B3 2대, 105동 U11 2대 </t>
+  </si>
+  <si>
+    <t>첨단부영1차</t>
+  </si>
+  <si>
+    <t>102동앞 6대 지상, 109동앞 5대 지상, 110동앞 6대 지상, 111동앞 6대 지상, 112동앞 4대 지상</t>
+  </si>
+  <si>
+    <t>첨단대라수어썸시티5차</t>
+  </si>
+  <si>
+    <t>3층 주차장 J9-L9 (병행5, 완속5), 4층 주차장 M10-L11 (전용3, 완속3), 3층 주차장 J7-J8 (병행7, 완속7), 4층 주차장 J8-J9 (전용3, 완속3), 3층 주차장 K6-N6 (병행7, 완속7), 4층 주차장 H2-I2 (전용3, 완속3), 4층 주차장 L4-L5 (전용2, 완속2), 4층 주차장 B4구역 (전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>첨단중해마루힐</t>
+  </si>
+  <si>
+    <t>102동 2층 3,4라인앞 (전용9, 완속9)</t>
+  </si>
+  <si>
+    <t>첨단에이엠시티 센트럴파크2차</t>
+  </si>
+  <si>
+    <t>201동 주차장(전용2, 완속2), 202동 주차장(전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>첨단부영2차</t>
+  </si>
+  <si>
+    <t>204동 7,8라인 앞(전용8, 완속8), 204동 3,4라인 앞(전용2, 완속2), 지하2주차장(전용1, 급속1), 203동 5,6라인 앞(전용2, 완속2), 202동 3,4라인 앞(전용2, 완속2)</t>
+  </si>
+  <si>
+    <t>첨단대라수1차</t>
+  </si>
+  <si>
+    <t>103동 지하1층 37,38구역 (전용2, 완속2), 102동 지하1층 41,42구역 (전용2, 완속2), 104동 지하1층 05,06구역 (전용2, 완속2), 101동 지하1층 01~03구역 (전용3, 완속3), 104동 2층 주차장 30~34구역 (병행3, 완속3), 103동 2층 주차장 25~26구역 (병행3, 완속3)</t>
+  </si>
+  <si>
+    <t>쌍암중흥s클래스리버시티</t>
+  </si>
+  <si>
+    <t>지하2층 104동 B03구역 (전용2, 병행4, 완속6), 103동 B01구역 (전용2, 병행4, 완속6), 102동 A17구역 (전용3, 급속1, 완속2), 101동 A01구역 (전용2, 병행4, 완속6), 101동 A03구역 (전용2, 병행4, 완속6)</t>
+  </si>
+  <si>
+    <t>첨단에이엠시티 센트럴파크1차</t>
+  </si>
+  <si>
+    <t>101동앞 2대 지상</t>
+  </si>
+  <si>
+    <t>첨단 중해마루힐 2차</t>
+  </si>
+  <si>
+    <t>203동 지하2층 출입구 (전용3, 급속1, 완속2), 203동 지하1층 출입구 (전용3, 급속1, 완속2), 203동 지상2층 출입구 (전용3, 급속1, 완속2)</t>
+  </si>
+  <si>
+    <t>첨단리젠시빌 3-5</t>
+  </si>
+  <si>
+    <t>상가동 앞(전용4, 완속4), 지하1주차장(전용3, 완속3), 지하2주차장(전용3, 완속3), 지하3주차장(전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>첨단부영e그린 1차</t>
+  </si>
+  <si>
+    <t>1104동 앞 (전용5, 병행6 / 급속1, 완속10)</t>
+  </si>
+  <si>
+    <t>첨단부영6차</t>
+  </si>
+  <si>
+    <t>1202동 앞 (전용11, 병행12, 급속1, 완속22), 지하4주차장 (병행2, 완속2), 지하6주차장 (병행2, 완속2)</t>
+  </si>
+  <si>
+    <t>첨단부영7차</t>
+  </si>
+  <si>
+    <t>1303동 앞 A (전용4, 병행6, 완속10), 1303동 앞 B (전용6, 병행2, 완속8), 지하1주차장 9구역 (병행2, 완속2), 지하2주차장 18구역 (병행2, 완속2), 지하3주차장 18구역 (병행2, 완속2), 지하4주차장 8구역 (병행2, 완속2), 지하5주차장 16구역 (병행2, 완속2)</t>
+  </si>
+  <si>
+    <t>쌍암동 대라수 주상복합 3차</t>
+  </si>
+  <si>
+    <t>지하1층 301동 1~2라인앞(B1~J1)(전용2, 병행7, 완속9), 지하3층 302동 1~2라인앞(병행5, 완속5), 지상2층 303동 3~4라인앞(병행5, 완속5)</t>
+  </si>
+  <si>
+    <t>힐스테이트첨단</t>
+  </si>
+  <si>
+    <t>지하4층 102동 출입구 옆 A(전용4, 완속3), 지하4층 102동 출입구 옆 B(전용2, 급속1), 지하4층 102동 출입구 옆 C(전용4, 완속2)</t>
+  </si>
+  <si>
+    <t>무들에코클래스</t>
+  </si>
+  <si>
+    <t>지상1층 (전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>쌍암동 대라수 주상복합 2차</t>
+  </si>
+  <si>
+    <t>201동 지상1층 01구역 (병행1, 완속1), 201동 지상1층 1~2라인 (병행1, 완속1), 201동 지상1층 10구역 (병행1, 완속1), 201동 지하1층 03구역 (전용2, 완속2), 201동 지상2층 04구역 (전용3, 완속3), 201동 지상3층 03구역 (병행3, 완속3)</t>
+  </si>
+  <si>
+    <t>첨단 LH3단지(행복주택)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3층 05 (전용2/급속 1), 1층 07 (전용4/완속1), </t>
+  </si>
+  <si>
+    <t>첨단 LH2단지(행복주택)</t>
+  </si>
+  <si>
+    <t>지상2층 계단실 옆(전용1, 완속1)</t>
+  </si>
+  <si>
+    <t>일신프레뷰</t>
+  </si>
+  <si>
+    <t>지상5층 (전용3, 완속3)</t>
+  </si>
+  <si>
+    <t>첨단 LH1단지(행복주택)</t>
+  </si>
+  <si>
+    <t>지상2층 05구역(전용1, 완속1)</t>
+  </si>
+  <si>
+    <t>연번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지번주소</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조사일자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노기섭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이승수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실태조사완료여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영기관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전용량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주광역시 광산구 삼도로 84-3</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 연산로 288</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 평동산단9번로 145</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송암길 1</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 빛동10로 22</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 빛동10로 23</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 평동로 639-22</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정로15번길 27</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 상무대로 268</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로 308</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 노안삼도로 1263</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 용동길63번길 31</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 상무대로 114</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 내상로15번길 23</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 상무대로 312</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 빛그린산단로 365</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정로 77</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 평동로1100번길 71</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로212번길 31-8</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정로85번길 10</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 도산로9번길 35</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 도산로 26</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로162번길 11-6</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정로 80</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로320번길 16-15</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 평동로1098번길 185</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 평동로1101번길 40</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 도산신송길 31</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 도산로12번길 17-25</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 도산로 3</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 남동길 15</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정로65번길 28</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 용보로27번길 46</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로182번길 15-11</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로181번길 30</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로182번길 16-3</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로182번길 15-12</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로212번길 54</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송도로320번길 11</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 내상로 80</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 남동길 18-10</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 도산로 28</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 평동로1119번길 25</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 광산로20번길 28</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 내상로 10</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정로 14</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 광산로30번길 65</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 오목내길 26</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 광산로 48-2</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 송정동 1005-1</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 광산로29번길 15</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 연산로 280</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로182번길 40</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 22-16</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 앰코로 11</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 19-20</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로106번길 25</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로152번길 81-15</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단강변로87번길 5</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단강변로 100</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 47</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로800번길 71</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 29-31</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 월계로 235-8</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 60-3</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로 773</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로 136</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 22-57</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로116번길 31</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로106번길 65-3</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로182번길 8</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로 96</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 월계로 203</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 앰코로 35</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 월계로 217</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 30</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단강변로99번길 22</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 월계로 175</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 19-7</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 29-32</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로170번길 59</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단월봉로 99</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로152번길 80</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단강변로 94</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 21-10</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로68번길 131</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 월계로 170</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로182번길 90</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 60-6</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로170번길 87</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로68번길 22</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 앰코로 21</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 월계로 223-8</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로182번길 50</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로182번길 76</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로68번길 99</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 산월로 81</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 산월로 64</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 산월로 80</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 22-77</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 60-5</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 22-54</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로800번길 11-5</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로825번길 9</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 임방울대로826번길 22-22</t>
+  </si>
+  <si>
+    <t>광주광역시 광산구 첨단중앙로152번길 6-8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1787,6 +2776,21 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1796,7 +2800,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1804,12 +2808,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2149,9 +3170,2891 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N110"/>
+  <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5.69140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.765625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="6.921875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.15234375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.61328125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.53515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="6.23046875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.53515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="6.61328125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.69140625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.07421875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.15234375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="14" width="45.53515625" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9.23046875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
+      <c r="M53" s="1"/>
+      <c r="N53" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+    </row>
+    <row r="55" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="N62" s="1" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+    </row>
+    <row r="71" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
+      <c r="K71" s="1"/>
+      <c r="L71" s="1"/>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1"/>
+    </row>
+    <row r="72" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+    </row>
+    <row r="73" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+      <c r="M73" s="1"/>
+      <c r="N73" s="1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+      <c r="M74" s="1"/>
+      <c r="N74" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+    </row>
+    <row r="77" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+    </row>
+    <row r="79" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
+      <c r="K79" s="1"/>
+      <c r="L79" s="1"/>
+      <c r="M79" s="1"/>
+      <c r="N79" s="1" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
+      <c r="K80" s="1"/>
+      <c r="L80" s="1"/>
+      <c r="M80" s="1"/>
+      <c r="N80" s="1" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+      <c r="M81" s="1"/>
+      <c r="N81" s="1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+      <c r="M82" s="1"/>
+      <c r="N82" s="1"/>
+    </row>
+    <row r="83" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+    </row>
+    <row r="86" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+    </row>
+    <row r="87" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="C88" s="1"/>
+      <c r="D88" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1"/>
+      <c r="J88" s="1"/>
+      <c r="K88" s="1"/>
+      <c r="L88" s="1"/>
+      <c r="M88" s="1"/>
+      <c r="N88" s="1" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E90" s="1"/>
+      <c r="F90" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="1"/>
+      <c r="N90" s="1" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C91" s="1"/>
+      <c r="D91" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="E91" s="1"/>
+      <c r="F91" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="1"/>
+      <c r="N91" s="1" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="E92" s="1"/>
+      <c r="F92" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="1"/>
+      <c r="N92" s="1" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+      <c r="N93" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C94" s="1"/>
+      <c r="D94" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="1"/>
+      <c r="N94" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C95" s="1"/>
+      <c r="D95" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="1"/>
+      <c r="N95" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C96" s="1"/>
+      <c r="D96" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="1"/>
+      <c r="N96" s="1" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="1"/>
+      <c r="N97" s="1" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="1"/>
+      <c r="M98" s="1"/>
+      <c r="N98" s="1" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C99" s="1"/>
+      <c r="D99" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1"/>
+      <c r="K99" s="1"/>
+      <c r="L99" s="1"/>
+      <c r="M99" s="1"/>
+      <c r="N99" s="1" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="D102" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="C103" s="1"/>
+      <c r="D103" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1"/>
+      <c r="J103" s="1"/>
+      <c r="K103" s="1"/>
+      <c r="L103" s="1"/>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="D104" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C105" s="1"/>
+      <c r="D105" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1"/>
+      <c r="J105" s="1"/>
+      <c r="K105" s="1"/>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C108" s="1"/>
+      <c r="D108" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1"/>
+      <c r="J108" s="1"/>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C109" s="1"/>
+      <c r="D109" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1"/>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1" t="s">
+        <v>784</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N1046"/>
   <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="2" max="2" width="26.61328125" customWidth="1"/>
+    <col min="3" max="3" width="12.921875" customWidth="1"/>
     <col min="4" max="4" width="31.84375" customWidth="1"/>
     <col min="5" max="5" width="19.61328125" customWidth="1"/>
     <col min="6" max="6" width="11.53515625" customWidth="1"/>
@@ -2159,6 +6062,8 @@
     <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="9" width="14.69140625" customWidth="1"/>
     <col min="10" max="10" width="13.765625" customWidth="1"/>
+    <col min="11" max="11" width="11.53515625" customWidth="1"/>
+    <col min="12" max="12" width="13.4609375" customWidth="1"/>
     <col min="13" max="13" width="14.765625" customWidth="1"/>
     <col min="14" max="14" width="18.53515625" customWidth="1"/>
   </cols>

--- a/조사1.xlsx
+++ b/조사1.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="선택된 충전소" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="280">
   <si>
     <t>조사자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,42 +34,18 @@
     <t>주차장(전용2, 완속2)</t>
   </si>
   <si>
-    <t>옥동 차량기지</t>
-  </si>
-  <si>
-    <t>정문옆(전용2, 급속2)</t>
-  </si>
-  <si>
-    <t>평동화물차고지</t>
-  </si>
-  <si>
-    <t>관리동앞 주차장(전용2, 급속2)</t>
-  </si>
-  <si>
     <t>국립야생동물질병관리원</t>
   </si>
   <si>
     <t>청사주차장(전용1, 급속1, 완속1)</t>
   </si>
   <si>
-    <t>친환경자동차 부품클러스터</t>
-  </si>
-  <si>
-    <t>글로벌비즈니스동 주차장(전용3, 급속2), 기술지원동 주차장(전용1, 급속2)</t>
-  </si>
-  <si>
     <t>광주친환경자동차인증센터(친환경자동차부품인증센터)</t>
   </si>
   <si>
     <t>주차장(급속1)</t>
   </si>
   <si>
-    <t>농업기술센터</t>
-  </si>
-  <si>
-    <t>본관 뒷편 주차장(전용1, 완속1), 제1주차장(전용4, 완속4)</t>
-  </si>
-  <si>
     <t>송정역 한국아델리움 더 씨티</t>
   </si>
   <si>
@@ -94,12 +70,6 @@
     <t>신관뒤 주차장(전용3, 완속3)</t>
   </si>
   <si>
-    <t>광산엘리체 레이크시티</t>
-  </si>
-  <si>
-    <t>102동 뒷편(전용11, 완속11), 104동 앞(전용5, 급속1, 완속4)</t>
-  </si>
-  <si>
     <t>송정서초등학교</t>
   </si>
   <si>
@@ -160,12 +130,6 @@
     <t>101동 옆 후문(전용5, 완속5)</t>
   </si>
   <si>
-    <t>도산 우미</t>
-  </si>
-  <si>
-    <t>102동 뒷편(전용4, 병행2, 완속6)</t>
-  </si>
-  <si>
     <t>도산호반2차</t>
   </si>
   <si>
@@ -304,24 +268,12 @@
     <t>1층 좌측 : 전용 1, 2층 중앙 : 전용 1, 2층 좌측 : 전용 2 / 충전2, 3층 중앙 : 전용 1, 4층 중앙 : 전용 1</t>
   </si>
   <si>
-    <t>송정5일시장 공영주차장</t>
-  </si>
-  <si>
-    <t>지상1층 : 전용8 / 충전4 (급4)</t>
-  </si>
-  <si>
     <t>광산CC 주차장</t>
   </si>
   <si>
     <t>출입구 좌측 : 전용2/충전2(급2)</t>
   </si>
   <si>
-    <t>광산로 제2공영주차장</t>
-  </si>
-  <si>
-    <t>주차장 맨끝: 전용4, 주차장 출구 우측: 전용1 / 충전1 (급1), 주차장 출구 좌측: 전용2 / 충전2 (급2)</t>
-  </si>
-  <si>
     <t xml:space="preserve">광주송정역뒤 공영주차장 </t>
   </si>
   <si>
@@ -487,12 +439,6 @@
     <t>원내주차장 1층(전용3, 완속3)</t>
   </si>
   <si>
-    <t>광주보훈병원</t>
-  </si>
-  <si>
-    <t>요양병원옆 체육관옆(전용6, 완속6), 고객주차장(전용12, 급속2, 완속10), 전용주차구역 1. 주차타워옥상(9) 2. 요양병원앞(4) 3. 장례식장(3) 4. 직원주차장(10)</t>
-  </si>
-  <si>
     <t>골드타워</t>
   </si>
   <si>
@@ -505,24 +451,12 @@
     <t>지상4층 4A구역(전용4, 급속1, 완속3)</t>
   </si>
   <si>
-    <t>첨단부영3차</t>
-  </si>
-  <si>
-    <t>관리동앞 3대 (지상), 302동앞 3대 (지상), 304동앞 3대 (지상), 305동앞 3대 (지상)</t>
-  </si>
-  <si>
     <t>쌍암힐스테이트리버파크</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;지하1층&gt;101동 E07 2대, 102동 C19 2대, 105동 V09 2대 &lt;지하2층&gt;105동 T12 3대, 105동 T10 2대, 105동 T09 1대, 101동 E13 2대, D13 2대, 101동 C13·14·15 콘센트형 3대, 101동 B2 2대, 102동 C21 2대, 105동 O12 콘센트형 2대 &lt;지하3층&gt;109동 B3 2대, 109동 B3 2대, 105동 U11 2대 </t>
   </si>
   <si>
-    <t>첨단부영1차</t>
-  </si>
-  <si>
-    <t>102동앞 6대 지상, 109동앞 5대 지상, 110동앞 6대 지상, 111동앞 6대 지상, 112동앞 4대 지상</t>
-  </si>
-  <si>
     <t>첨단대라수어썸시티5차</t>
   </si>
   <si>
@@ -541,12 +475,6 @@
     <t>201동 주차장(전용2, 완속2), 202동 주차장(전용2, 완속2)</t>
   </si>
   <si>
-    <t>첨단부영2차</t>
-  </si>
-  <si>
-    <t>204동 7,8라인 앞(전용8, 완속8), 204동 3,4라인 앞(전용2, 완속2), 지하2주차장(전용1, 급속1), 203동 5,6라인 앞(전용2, 완속2), 202동 3,4라인 앞(전용2, 완속2)</t>
-  </si>
-  <si>
     <t>첨단대라수1차</t>
   </si>
   <si>
@@ -569,30 +497,6 @@
   </si>
   <si>
     <t>203동 지하2층 출입구 (전용3, 급속1, 완속2), 203동 지하1층 출입구 (전용3, 급속1, 완속2), 203동 지상2층 출입구 (전용3, 급속1, 완속2)</t>
-  </si>
-  <si>
-    <t>첨단리젠시빌 3-5</t>
-  </si>
-  <si>
-    <t>상가동 앞(전용4, 완속4), 지하1주차장(전용3, 완속3), 지하2주차장(전용3, 완속3), 지하3주차장(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>첨단부영e그린 1차</t>
-  </si>
-  <si>
-    <t>1104동 앞 (전용5, 병행6 / 급속1, 완속10)</t>
-  </si>
-  <si>
-    <t>첨단부영6차</t>
-  </si>
-  <si>
-    <t>1202동 앞 (전용11, 병행12, 급속1, 완속22), 지하4주차장 (병행2, 완속2), 지하6주차장 (병행2, 완속2)</t>
-  </si>
-  <si>
-    <t>첨단부영7차</t>
-  </si>
-  <si>
-    <t>1303동 앞 A (전용4, 병행6, 완속10), 1303동 앞 B (전용6, 병행2, 완속8), 지하1주차장 9구역 (병행2, 완속2), 지하2주차장 18구역 (병행2, 완속2), 지하3주차장 18구역 (병행2, 완속2), 지하4주차장 8구역 (병행2, 완속2), 지하5주차장 16구역 (병행2, 완속2)</t>
   </si>
   <si>
     <t>쌍암동 대라수 주상복합 3차</t>
@@ -695,322 +599,280 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>광주광역시 광산구 삼도로 84-3</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 연산로 288</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 평동산단9번로 145</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송암길 1</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 빛동10로 22</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 빛동10로 23</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 평동로 639-22</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정로15번길 27</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 상무대로 268</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로 308</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 노안삼도로 1263</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 용동길63번길 31</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 상무대로 114</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 내상로15번길 23</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 상무대로 312</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 빛그린산단로 365</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정로 77</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 평동로1100번길 71</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로212번길 31-8</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정로85번길 10</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 도산로9번길 35</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 도산로 26</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로162번길 11-6</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정로 80</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로320번길 16-15</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 평동로1098번길 185</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 평동로1101번길 40</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 도산신송길 31</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 도산로12번길 17-25</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 도산로 3</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 남동길 15</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정로65번길 28</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 용보로27번길 46</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로182번길 15-11</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로181번길 30</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로182번길 16-3</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로182번길 15-12</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로212번길 54</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송도로320번길 11</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 내상로 80</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 남동길 18-10</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 도산로 28</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 평동로1119번길 25</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 광산로20번길 28</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 내상로 10</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정로 14</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 광산로30번길 65</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 오목내길 26</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 광산로 48-2</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 송정동 1005-1</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 광산로29번길 15</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 연산로 280</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로182번길 40</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 22-16</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 앰코로 11</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 19-20</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로106번길 25</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로152번길 81-15</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단강변로87번길 5</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단강변로 100</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 47</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로800번길 71</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 29-31</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 월계로 235-8</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 60-3</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로 773</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로 136</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 22-57</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로116번길 31</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로106번길 65-3</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로182번길 8</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로 96</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 월계로 203</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 앰코로 35</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 월계로 217</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 30</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단강변로99번길 22</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 월계로 175</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 19-7</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 29-32</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로170번길 59</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단월봉로 99</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로152번길 80</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단강변로 94</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 21-10</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로68번길 131</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 월계로 170</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로182번길 90</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 60-6</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로170번길 87</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로68번길 22</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 앰코로 21</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 월계로 223-8</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로182번길 50</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로182번길 76</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로68번길 99</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 산월로 81</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 산월로 64</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 산월로 80</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 22-77</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 60-5</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 22-54</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로800번길 11-5</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로825번길 9</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 임방울대로826번길 22-22</t>
-  </si>
-  <si>
-    <t>광주광역시 광산구 첨단중앙로152번길 6-8</t>
+    <t>광주 광산구 첨단중앙로182번길 40</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 22-16</t>
+  </si>
+  <si>
+    <t>광주 광산구 앰코로 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 19-20</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로106번길 25</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로152번길 81-15</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단강변로87번길 5</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 47</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로800번길 71</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 29-31</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 235-8</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 60-3</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 773</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로 136</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 22-57</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로116번길 31</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로106번길 65-3</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로 96</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 203</t>
+  </si>
+  <si>
+    <t>광주 광산구 앰코로 35</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 217</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 30</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단강변로99번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 175</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 19-7</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 29-32</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로170번길 59</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로152번길 80</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단강변로 94</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 21-10</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단강변로 100</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로182번길 90</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 60-6</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로170번길 87</t>
+  </si>
+  <si>
+    <t>광주 광산구 앰코로 21</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 223-8</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로182번길 50</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로182번길 76</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 22-77</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로182번길 8</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 60-5</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 22-54</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로800번길 11-5</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로825번길 9</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로826번길 22-22</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로152번길 6-8</t>
+  </si>
+  <si>
+    <t>광주 광산구 삼도로 84-3</t>
+  </si>
+  <si>
+    <t>광주 광산구 송암길 1</t>
+  </si>
+  <si>
+    <t>광주 광산구 빛동10로 23</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정로15번길 27</t>
+  </si>
+  <si>
+    <t>광주 광산구 상무대로 268</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로 308</t>
+  </si>
+  <si>
+    <t>광주 광산구 노안삼도로 1263</t>
+  </si>
+  <si>
+    <t>광주 광산구 상무대로 114</t>
+  </si>
+  <si>
+    <t>광주 광산구 내상로15번길 23</t>
+  </si>
+  <si>
+    <t>광주 광산구 상무대로 312</t>
+  </si>
+  <si>
+    <t>광주 광산구 빛그린산단로 365</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정로 77</t>
+  </si>
+  <si>
+    <t>광주 광산구 평동로1100번길 71</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로212번길 31-8</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정로85번길 10</t>
+  </si>
+  <si>
+    <t>광주 광산구 용동길63번길 31</t>
+  </si>
+  <si>
+    <t>광주 광산구 도산로9번길 35</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로162번길 11-6</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정로 80</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로320번길 16-15</t>
+  </si>
+  <si>
+    <t>광주 광산구 평동로1098번길 185</t>
+  </si>
+  <si>
+    <t>광주 광산구 평동로1101번길 40</t>
+  </si>
+  <si>
+    <t>광주 광산구 도산신송길 31</t>
+  </si>
+  <si>
+    <t>광주 광산구 도산로12번길 17-25</t>
+  </si>
+  <si>
+    <t>광주 광산구 도산로 3</t>
+  </si>
+  <si>
+    <t>광주 광산구 남동길 15</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정로65번길 28</t>
+  </si>
+  <si>
+    <t>광주 광산구 용보로27번길 46</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로182번길 15-11</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로181번길 30</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로182번길 16-3</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로182번길 15-12</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로212번길 54</t>
+  </si>
+  <si>
+    <t>광주 광산구 송도로320번길 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 내상로 80</t>
+  </si>
+  <si>
+    <t>광주 광산구 남동길 18-10</t>
+  </si>
+  <si>
+    <t>광주 광산구 도산로 28</t>
+  </si>
+  <si>
+    <t>광주 광산구 평동로1119번길 25</t>
+  </si>
+  <si>
+    <t>광주 광산구 광산로20번길 28</t>
+  </si>
+  <si>
+    <t>광주 광산구 내상로 10</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정로 14</t>
+  </si>
+  <si>
+    <t>광주 광산구 오목내길 26</t>
+  </si>
+  <si>
+    <t>광주 광산구 송정동 1005-1</t>
+  </si>
+  <si>
+    <t>광주 광산구 광산로29번길 15</t>
+  </si>
+  <si>
+    <t>광주 광산구 연산로 280</t>
+  </si>
+  <si>
+    <t>지하1층 (전용3,완속3)</t>
   </si>
 </sst>
 </file>
@@ -1048,12 +910,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1083,15 +951,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1426,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.69140625" style="2" customWidth="1"/>
@@ -1448,44 +1348,44 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -1497,11 +1397,11 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1523,11 +1423,11 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1549,11 +1449,11 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1575,11 +1475,11 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1601,11 +1501,11 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1627,11 +1527,11 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1653,11 +1553,11 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1679,11 +1579,11 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1705,11 +1605,11 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1731,11 +1631,11 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1757,11 +1657,11 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1783,11 +1683,11 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1809,11 +1709,11 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1835,11 +1735,11 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1861,11 +1761,11 @@
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1887,11 +1787,11 @@
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1913,11 +1813,11 @@
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1939,11 +1839,11 @@
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1965,11 +1865,11 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1991,11 +1891,11 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -2017,11 +1917,11 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -2043,11 +1943,11 @@
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -2069,11 +1969,11 @@
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -2095,11 +1995,11 @@
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -2108,24 +2008,22 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="N25" s="1"/>
     </row>
     <row r="26" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -2135,7 +2033,7 @@
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2143,15 +2041,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2161,7 +2059,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2169,15 +2067,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2187,7 +2085,7 @@
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2195,15 +2093,15 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -2213,7 +2111,7 @@
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2221,15 +2119,15 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2239,7 +2137,7 @@
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2247,15 +2145,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2264,7 +2162,9 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
+      <c r="N31" s="1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
@@ -2275,11 +2175,11 @@
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2301,11 +2201,11 @@
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2327,11 +2227,11 @@
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2353,11 +2253,11 @@
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2379,11 +2279,11 @@
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2405,11 +2305,11 @@
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2418,24 +2318,22 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="N37" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -2445,7 +2343,7 @@
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2453,15 +2351,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2471,7 +2369,7 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2479,15 +2377,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2497,7 +2395,7 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2505,15 +2403,15 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2523,7 +2421,7 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2531,15 +2429,15 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2549,7 +2447,7 @@
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2557,15 +2455,15 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -2574,7 +2472,9 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
+      <c r="N43" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
@@ -2585,11 +2485,11 @@
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2611,11 +2511,11 @@
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2637,11 +2537,11 @@
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2650,24 +2550,22 @@
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
-      <c r="N46" s="1" t="s">
-        <v>89</v>
-      </c>
+      <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>90</v>
+      <c r="B47" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2677,7 +2575,7 @@
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2685,15 +2583,15 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>265</v>
+        <v>189</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2703,7 +2601,7 @@
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2711,15 +2609,15 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2729,7 +2627,7 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2737,15 +2635,15 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>267</v>
+        <v>191</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2755,7 +2653,7 @@
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2763,15 +2661,15 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>268</v>
+        <v>192</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2781,7 +2679,7 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2789,15 +2687,15 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2807,7 +2705,7 @@
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2815,15 +2713,15 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>270</v>
+        <v>194</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2833,7 +2731,7 @@
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2841,15 +2739,15 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2858,22 +2756,24 @@
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
+      <c r="N54" s="1" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2883,7 +2783,7 @@
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2891,15 +2791,15 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>273</v>
+        <v>197</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2909,7 +2809,7 @@
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
-        <v>108</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -2921,11 +2821,11 @@
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>274</v>
+        <v>198</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -2947,11 +2847,11 @@
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>275</v>
+        <v>199</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -2973,11 +2873,11 @@
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>276</v>
+        <v>200</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -2999,11 +2899,11 @@
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -3025,11 +2925,11 @@
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>278</v>
+        <v>202</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -3038,24 +2938,22 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
-      <c r="N61" s="1" t="s">
-        <v>118</v>
-      </c>
+      <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
-        <v>279</v>
+        <v>203</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -3064,24 +2962,22 @@
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
-      <c r="N62" s="1" t="s">
-        <v>120</v>
-      </c>
+      <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>280</v>
+        <v>204</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -3090,24 +2986,22 @@
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
-      <c r="N63" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -3117,7 +3011,7 @@
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3129,11 +3023,11 @@
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>282</v>
+        <v>206</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -3142,22 +3036,24 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
+      <c r="N65" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="66" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -3166,9 +3062,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
-      <c r="N66" s="1" t="s">
-        <v>126</v>
-      </c>
+      <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
@@ -3179,11 +3073,11 @@
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -3205,11 +3099,11 @@
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
-        <v>285</v>
+        <v>209</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -3218,24 +3112,22 @@
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
-      <c r="N68" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>286</v>
+        <v>210</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -3245,7 +3137,7 @@
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3253,15 +3145,15 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
-        <v>287</v>
+        <v>211</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -3270,7 +3162,9 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
+      <c r="N70" s="1" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="71" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
@@ -3281,11 +3175,11 @@
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1" t="s">
-        <v>288</v>
+        <v>212</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -3294,22 +3188,24 @@
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
+      <c r="N71" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="72" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -3325,15 +3221,15 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>290</v>
+        <v>214</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -3343,7 +3239,7 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3351,15 +3247,15 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>291</v>
+        <v>215</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -3368,9 +3264,7 @@
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
-      <c r="N74" s="1" t="s">
-        <v>139</v>
-      </c>
+      <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
@@ -3381,11 +3275,11 @@
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
-        <v>292</v>
+        <v>216</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -3394,24 +3288,22 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
-      <c r="N75" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="N75" s="1"/>
     </row>
     <row r="76" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -3420,7 +3312,9 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
+      <c r="N76" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="77" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
@@ -3430,12 +3324,12 @@
         <v>143</v>
       </c>
       <c r="C77" s="1"/>
-      <c r="D77" s="1" t="s">
-        <v>294</v>
+      <c r="D77" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -3453,15 +3347,15 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="C78" s="1"/>
-      <c r="D78" s="1" t="s">
-        <v>295</v>
+      <c r="D78" s="3" t="s">
+        <v>218</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -3470,22 +3364,24 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
+      <c r="N78" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="79" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1" t="s">
-        <v>296</v>
+        <v>219</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -3495,7 +3391,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3503,15 +3399,15 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1" t="s">
-        <v>297</v>
+        <v>220</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -3521,7 +3417,7 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3529,15 +3425,15 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>298</v>
+        <v>221</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -3547,7 +3443,7 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="82" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3555,15 +3451,15 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -3572,7 +3468,9 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
+      <c r="N82" s="1" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="83" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
@@ -3583,11 +3481,11 @@
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>300</v>
+        <v>223</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -3609,11 +3507,11 @@
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -3635,11 +3533,11 @@
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>302</v>
+        <v>225</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -3648,22 +3546,24 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
-      <c r="N85" s="1"/>
+      <c r="N85" s="1" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="86" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>303</v>
+        <v>226</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -3672,22 +3572,24 @@
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
-      <c r="N86" s="1"/>
+      <c r="N86" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="87" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C87" s="1"/>
-      <c r="D87" s="1" t="s">
-        <v>304</v>
+      <c r="D87" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -3697,7 +3599,7 @@
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3705,15 +3607,15 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="C88" s="1"/>
-      <c r="D88" s="1" t="s">
-        <v>305</v>
+      <c r="D88" s="3" t="s">
+        <v>227</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -3723,7 +3625,7 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -3735,11 +3637,11 @@
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -3761,11 +3663,11 @@
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1" t="s">
-        <v>306</v>
+        <v>229</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -3787,11 +3689,11 @@
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -3813,11 +3715,11 @@
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1" t="s">
-        <v>308</v>
+        <v>231</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -3839,11 +3741,11 @@
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
-        <v>309</v>
+        <v>232</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -3865,11 +3767,11 @@
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>310</v>
+        <v>233</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -3882,424 +3784,17 @@
         <v>174</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
-        <v>94</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
-      <c r="N95" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
-        <v>95</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-      <c r="K96" s="1"/>
-      <c r="L96" s="1"/>
-      <c r="M96" s="1"/>
-      <c r="N96" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
-        <v>96</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-      <c r="K97" s="1"/>
-      <c r="L97" s="1"/>
-      <c r="M97" s="1"/>
-      <c r="N97" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
-        <v>97</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G98" s="1"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
-      <c r="J98" s="1"/>
-      <c r="K98" s="1"/>
-      <c r="L98" s="1"/>
-      <c r="M98" s="1"/>
-      <c r="N98" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
-        <v>98</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G99" s="1"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="1"/>
-      <c r="M99" s="1"/>
-      <c r="N99" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
-        <v>99</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
-      <c r="N100" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
-        <v>100</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G101" s="1"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
-      <c r="J101" s="1"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="1"/>
-      <c r="M101" s="1"/>
-      <c r="N101" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
-        <v>101</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-      <c r="L102" s="1"/>
-      <c r="M102" s="1"/>
-      <c r="N102" s="1" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
-        <v>102</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
-      <c r="N103" s="1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="104" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
-        <v>103</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G104" s="1"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
-      <c r="J104" s="1"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="1"/>
-      <c r="M104" s="1"/>
-      <c r="N104" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="105" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
-        <v>104</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G105" s="1"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
-      <c r="J105" s="1"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="1"/>
-      <c r="M105" s="1"/>
-      <c r="N105" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
-        <v>105</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G106" s="1"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
-      <c r="J106" s="1"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
-      <c r="N106" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="107" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="1">
-        <v>106</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-      <c r="N107" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="1">
-        <v>107</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
-      <c r="N108" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="1">
-        <v>108</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G109" s="1"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
-      <c r="J109" s="1"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="1"/>
-      <c r="M109" s="1"/>
-      <c r="N109" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="1">
-        <v>109</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G110" s="1"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
-      <c r="J110" s="1"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="1"/>
-      <c r="M110" s="1"/>
-      <c r="N110" s="1" t="s">
-        <v>206</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D79:D87 D47:D77 D89:D94">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D78">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D46">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/조사1.xlsx
+++ b/조사1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="430">
   <si>
     <t>조사자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -873,6 +873,457 @@
   </si>
   <si>
     <t>지하1층 (전용3,완속3)</t>
+  </si>
+  <si>
+    <t>농협하나로유통(수완)</t>
+  </si>
+  <si>
+    <t>수영빌딩</t>
+  </si>
+  <si>
+    <t>성덕주차타워</t>
+  </si>
+  <si>
+    <t>수완센트럴병원</t>
+  </si>
+  <si>
+    <t>주차장</t>
+  </si>
+  <si>
+    <t>샤브올데이</t>
+  </si>
+  <si>
+    <t>애플타워주차장</t>
+  </si>
+  <si>
+    <t>더블유여성병원</t>
+  </si>
+  <si>
+    <t>세계로 365병원</t>
+  </si>
+  <si>
+    <t>남궁빌딩</t>
+  </si>
+  <si>
+    <t>국선빌딩</t>
+  </si>
+  <si>
+    <t>KS병원</t>
+  </si>
+  <si>
+    <t>BYC 광주수완빌딩</t>
+  </si>
+  <si>
+    <t>수완에너지주식회사</t>
+  </si>
+  <si>
+    <t>광주고실초등학교</t>
+  </si>
+  <si>
+    <t>새별초등학교</t>
+  </si>
+  <si>
+    <t>성덕중학교</t>
+  </si>
+  <si>
+    <t>장덕중학교</t>
+  </si>
+  <si>
+    <t>수완하나중학교</t>
+  </si>
+  <si>
+    <t>고실중학교</t>
+  </si>
+  <si>
+    <t>장덕고등학교</t>
+  </si>
+  <si>
+    <t>성덕고등학교</t>
+  </si>
+  <si>
+    <t>수완고등학교</t>
+  </si>
+  <si>
+    <t>수완대성베르힐</t>
+  </si>
+  <si>
+    <t>성덕마을새한포유</t>
+  </si>
+  <si>
+    <t>수완GS자이</t>
+  </si>
+  <si>
+    <t>신가2차호반리젠시빌</t>
+  </si>
+  <si>
+    <t>수완코오롱하늘채</t>
+  </si>
+  <si>
+    <t>신안실크밸리</t>
+  </si>
+  <si>
+    <t>수완휴먼시아5단지</t>
+  </si>
+  <si>
+    <t>수완이지더원</t>
+  </si>
+  <si>
+    <t>수완양우내안애 1차</t>
+  </si>
+  <si>
+    <t>수완 우미린2차</t>
+  </si>
+  <si>
+    <t>수완 영무예다음 2차</t>
+  </si>
+  <si>
+    <t>모아엘가 수완</t>
+  </si>
+  <si>
+    <t>성덕마을 대방노블랜드 5차</t>
+  </si>
+  <si>
+    <t>수완대주피오레</t>
+  </si>
+  <si>
+    <t>신가주공</t>
+  </si>
+  <si>
+    <t>수완2차중흥</t>
+  </si>
+  <si>
+    <t>수완휴먼시아 4단지</t>
+  </si>
+  <si>
+    <t>수완휴먼시아 6단지</t>
+  </si>
+  <si>
+    <t>진흥더루벤스</t>
+  </si>
+  <si>
+    <t>수완휴먼시아 1단지</t>
+  </si>
+  <si>
+    <t>아름마을휴먼시아 2단지</t>
+  </si>
+  <si>
+    <t>수완1차 중흥</t>
+  </si>
+  <si>
+    <t>수완 대방노블랜드</t>
+  </si>
+  <si>
+    <t>수완 대방3차</t>
+  </si>
+  <si>
+    <t>수완 호반베르디움 2차</t>
+  </si>
+  <si>
+    <t>수완골드클래스2차</t>
+  </si>
+  <si>
+    <t>수완영무예다음</t>
+  </si>
+  <si>
+    <t>수완문화체육센터(체육진흥과-지상)</t>
+  </si>
+  <si>
+    <t>수완문화체육센터(교통지도과-지하/체육과-지상)</t>
+  </si>
+  <si>
+    <t>광주 명진고등학교</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 261</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로 85</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로 120</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로 6</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로50번길 20-3</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로 160</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 330</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 331</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로 77</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 348</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 342</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로 220</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로 52</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로 130</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로 300</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로 125</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로 65</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로105번길 47</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로229번길 30</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로 45</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로 75</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로 155</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로94번길 31</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로170번길 39-9</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로95번길 45</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로 205</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로137번길 39</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로330번길 34</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로145번길 42</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로101번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로330번길 16</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로132번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로33번길 79</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로381번길 27</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로170번길 39-26</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로170번길 39-25</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로 204</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로145번길 15</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로145번길 43</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로329번길 51</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로6번길 35</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로123번길 70</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로123번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로76번길 74</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로76번길 40</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로170번길 39-10</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로329번길 19</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로 285</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로95번길 15</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로132번길 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로12번길 21</t>
+  </si>
+  <si>
+    <t>정은진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8대 (급속1대) (완속7대), 1대 (급속), 10대 (급속)</t>
+  </si>
+  <si>
+    <t>2대 C02 (지하1층), 2대 C03, 5대 D02</t>
+  </si>
+  <si>
+    <t>2층 (전용1/충전1) 비상구앞</t>
+  </si>
+  <si>
+    <t>1층 1대</t>
+  </si>
+  <si>
+    <t>1층 주차장 (전용4/충전4)</t>
+  </si>
+  <si>
+    <t>지하1층 2대</t>
+  </si>
+  <si>
+    <t>지상 입구앞 (2대)</t>
+  </si>
+  <si>
+    <t>주차장입구 1대</t>
+  </si>
+  <si>
+    <t>지상 주차장입구 1대</t>
+  </si>
+  <si>
+    <t>교문입구 1대</t>
+  </si>
+  <si>
+    <t>지상 (안내옆) 1대</t>
+  </si>
+  <si>
+    <t>운동장옆 지상 1대</t>
+  </si>
+  <si>
+    <t>교문옆 1대</t>
+  </si>
+  <si>
+    <t>지상1대 연못뒤</t>
+  </si>
+  <si>
+    <t>교문앞 1대</t>
+  </si>
+  <si>
+    <t>교문입구 바로옆 1대</t>
+  </si>
+  <si>
+    <t>지상 (전용 5 충전 5) 102동앞, 지상 (전용 3 충전 3) 105동앞, 지상 (전용 5 충전 5) 103동앞</t>
+  </si>
+  <si>
+    <t>지상 (전용 6 충전 6) 105동 앞, 지상 (전용 3 충전 3) 104동 앞</t>
+  </si>
+  <si>
+    <t>지하1층 (전용7 충전1) C18구역, 지하1층 (전용2 충전2) A4구역, 지하1층 (전용2 충전2) A8구역, 지하1층 (전용2 충전2) B17구역, 지하1층 (전용2 충전2) A6구역, 지하1층 (전용2 충전2) B19구역, 지하1층 (전용2 충전2) A5구역, 지하2층 (전용4 충전4) 병행4 H19구역, 지하2층 (전용3 충전3) 병행3 H4구역</t>
+  </si>
+  <si>
+    <t>지상(전용3 충전3) 201동앞, 지상(전용3 충전3) 202동앞 (병행3)</t>
+  </si>
+  <si>
+    <t>지하1층 108~109동 사이: 전용2/충전2, 지하2층 A23: 전용3/충전3, 지하2층 A80: 전용1/충전1, 지하2층 A40: 전용4/충전4, 지하2층 A29: 전용9/충전9, 지하2층 A38: 전용2/충전2, 지하2층 A39: 전용4/충전4</t>
+  </si>
+  <si>
+    <t>104동 2대 (C10) 지하, 106동 2대 (D20) 지하, 102동 1대 (A19) 지하, 105동 5대 지상, 110동 5대 지상</t>
+  </si>
+  <si>
+    <t>지하3동 : 전용3/충전3, 502동앞 : 전용3, 502동앞(분리수거장옆) : 전용 6/충전3, 503동앞 : 전용4</t>
+  </si>
+  <si>
+    <t>지상 (전용2 충전2) 105동 1문앞, 지상 (전용3 충전3) 103동 1문앞, 지상 (전용3 충전3) 정문 좌측, 지상 (전용4 충전4) 정문 우측</t>
+  </si>
+  <si>
+    <t>지하1층 (겸용 5 충전 5) A01구역, 지상 (전용 3 충전 3) 103동 앞, 지상 (전용 3 충전 3) 102동 앞</t>
+  </si>
+  <si>
+    <t>지상 (전용 3 충전 3) 211동앞, 지상 (전용 3 충전 3) 211동앞, 지상 (전용 3 충전 3) 208동앞, 지상 (전용 3 충전 3) 208동앞, 지상 (전용 3 충전 3) 201동앞, 지상 (전용 3 충전 3) 205동앞, 지하 (전용 3 충전 3) 25구역 (겸용 3), 지하 (전용 3 충전 3) 혼용 1, 지하 (3) 197구역, 지하 (3) R62 (병행 3)</t>
+  </si>
+  <si>
+    <t>지하1층 (전용 5 충전 5) 병행 4대 F구역, 지하1층 (전용 2 충전 2) 병행 1대 H구역, 지하1층 (전용 3 충전 3) A구역</t>
+  </si>
+  <si>
+    <t xml:space="preserve">① 지하(전용 1 충전 1) B42구역, ② 지하(전용 1 충전 1) R22구역, ③ 지하(전용 1 충전 1) 107동 입구 R37구역, ④ 지하(전용 1 충전 1) Y72구역, 지하(전용 1 충전 1) Y56구역, ⑤ 지하(전용 1 충전 1) R54구역, ⑥ 지상(전용 4 충전 4) 104동앞, ⑦ 지상(전용 4 충전 4) 104동앞, ⑧ 지상(전용 1 충전 1) 아파트입구 </t>
+  </si>
+  <si>
+    <t>지상 (겸용 2 충전 2) 504동 뒤, 지하 2층 (전용 15 충전 15) 겸용 3 17구역 겸용 2 (30구역), 지하 2층 (전용 3 충전3) 42구역</t>
+  </si>
+  <si>
+    <t>관리동앞 4대, 103동앞 3대, 104동앞 3대, 102동앞 2대(병행)</t>
+  </si>
+  <si>
+    <t>104동 앞 : 전용18/충전7</t>
+  </si>
+  <si>
+    <t>지하 (전용3 충전3) 병행 2 B23, 지하 (전용2 충전2) A19, 지하 (전용 4 충전4) 병행3 A68, 지하 (전용2 충전2) A71</t>
+  </si>
+  <si>
+    <t>406동앞 : 전용7/충전7, 402동앞 : 전용2/충전2, 403동앞 : 전용2/충전2</t>
+  </si>
+  <si>
+    <t>602동 6개, 610동 9개, 지하 601동 1개, 603동 1개(C4), 607동 1개(B1), 608동 1개(A3), 604동 1개(A4)</t>
+  </si>
+  <si>
+    <t>지하 (전용 6 충전 6) 병행 6, 지상 (전용 5 충전 5) 106동앞, 지상 (전용 10 충전 10) 급속 1 106동앞 (병행 2), 지상 (전용 1 충전1) 106동뒤</t>
+  </si>
+  <si>
+    <t>101동 앞 : 전용3/충전 1, 1지하주차장 : 전용3/충전 3, 2지하주차장 : 전용7/충전 7, 106동 후면 : 전용 2, 107동 후면 : 전용 2, 105동 후면 : 전용 2, 108동 후면 : 전용 3, 102동 후면 : 전용 2, 104동 측면 : 전용 3</t>
+  </si>
+  <si>
+    <t>213동 앞 : 전용 8/충전 8, 3지하주차장 : 전용 4/충전 4, 2지하주차장 : 전용 3/충전 3, 1지하주차장 : 전용 3/충전 3</t>
+  </si>
+  <si>
+    <t>관리동 옆 지하 전용3/충전3, 111동 후면 지하 전용2/충전2, 109동 옆 지하 전용2/충전2, 112동 옆 지하 전용3/충전3</t>
+  </si>
+  <si>
+    <t>108동 앞 전용3/충전3, 105동 앞 전용3/충전3, 103동 앞 전용6/충전6, 103동 후면 : 전용2/충전2, 102동 앞 : 전용1/충전1, 101동 앞 : 전용3/충전3</t>
+  </si>
+  <si>
+    <t>301동 3대, 306동 2대, 303동 3개</t>
+  </si>
+  <si>
+    <t>203동 1대, 206동 1대, 209동 1대</t>
+  </si>
+  <si>
+    <t>204동 지하2대, 210동 4대 (지상)</t>
+  </si>
+  <si>
+    <t>102동앞: 지상 전용5/충전5, 지하 101동: 전용2/충전2, 지하 102동: 전용2/충전2</t>
+  </si>
+  <si>
+    <t>지하1층 (전용1 충전1)급속1, 지하1층 (전용3) &lt;교통지도과&gt;, 지상 (전용3) &lt;체육진흥과&gt;</t>
   </si>
 </sst>
 </file>
@@ -951,16 +1402,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1326,7 +1788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N94"/>
+  <dimension ref="A1:N149"/>
   <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.69140625" style="2" customWidth="1"/>
@@ -3784,15 +4246,1380 @@
         <v>174</v>
       </c>
     </row>
+    <row r="95" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C95" s="4"/>
+      <c r="D95" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="E95" s="4"/>
+      <c r="F95" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="4"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="4"/>
+      <c r="N95" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C96" s="4"/>
+      <c r="D96" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="4"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="4"/>
+      <c r="N96" s="4"/>
+    </row>
+    <row r="97" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C97" s="4"/>
+      <c r="D97" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G97" s="4"/>
+      <c r="H97" s="4"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="4"/>
+      <c r="N97" s="4"/>
+    </row>
+    <row r="98" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C98" s="4"/>
+      <c r="D98" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C99" s="4"/>
+      <c r="D99" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+    </row>
+    <row r="100" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C100" s="4"/>
+      <c r="D100" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C101" s="4"/>
+      <c r="D101" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+    </row>
+    <row r="102" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C102" s="4"/>
+      <c r="D102" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C103" s="4"/>
+      <c r="D103" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+    </row>
+    <row r="104" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C104" s="4"/>
+      <c r="D104" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+    </row>
+    <row r="105" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C105" s="4"/>
+      <c r="D105" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+    </row>
+    <row r="106" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C106" s="4"/>
+      <c r="D106" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C108" s="4"/>
+      <c r="D108" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C109" s="4"/>
+      <c r="D109" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="1">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="C110" s="4"/>
+      <c r="D110" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="1">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C111" s="4"/>
+      <c r="D111" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="1">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="C112" s="4"/>
+      <c r="D112" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="1">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C113" s="4"/>
+      <c r="D113" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="1">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C114" s="4"/>
+      <c r="D114" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="1">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C115" s="4"/>
+      <c r="D115" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="1">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C116" s="4"/>
+      <c r="D116" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="1">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="4"/>
+      <c r="D117" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="1">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C118" s="4"/>
+      <c r="D118" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E118" s="4"/>
+      <c r="F118" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="4"/>
+      <c r="N118" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="1">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C119" s="4"/>
+      <c r="D119" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="4"/>
+      <c r="N119" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="1">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C120" s="4"/>
+      <c r="D120" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E120" s="4"/>
+      <c r="F120" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G120" s="4"/>
+      <c r="H120" s="4"/>
+      <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
+      <c r="K120" s="4"/>
+      <c r="L120" s="4"/>
+      <c r="M120" s="4"/>
+      <c r="N120" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="1">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C121" s="4"/>
+      <c r="D121" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="E121" s="4"/>
+      <c r="F121" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G121" s="4"/>
+      <c r="H121" s="4"/>
+      <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
+      <c r="K121" s="4"/>
+      <c r="L121" s="4"/>
+      <c r="M121" s="4"/>
+      <c r="N121" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="1">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="C122" s="4"/>
+      <c r="D122" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E122" s="4"/>
+      <c r="F122" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G122" s="4"/>
+      <c r="H122" s="4"/>
+      <c r="I122" s="4"/>
+      <c r="J122" s="4"/>
+      <c r="K122" s="4"/>
+      <c r="L122" s="4"/>
+      <c r="M122" s="4"/>
+      <c r="N122" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="1">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C123" s="4"/>
+      <c r="D123" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E123" s="4"/>
+      <c r="F123" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G123" s="4"/>
+      <c r="H123" s="4"/>
+      <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
+      <c r="K123" s="4"/>
+      <c r="L123" s="4"/>
+      <c r="M123" s="4"/>
+      <c r="N123" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="1">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C124" s="4"/>
+      <c r="D124" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="E124" s="4"/>
+      <c r="F124" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G124" s="4"/>
+      <c r="H124" s="4"/>
+      <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
+      <c r="K124" s="4"/>
+      <c r="L124" s="4"/>
+      <c r="M124" s="4"/>
+      <c r="N124" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="1">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C125" s="4"/>
+      <c r="D125" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E125" s="4"/>
+      <c r="F125" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G125" s="4"/>
+      <c r="H125" s="4"/>
+      <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
+      <c r="K125" s="4"/>
+      <c r="L125" s="4"/>
+      <c r="M125" s="4"/>
+      <c r="N125" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="1">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C126" s="4"/>
+      <c r="D126" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+      <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
+      <c r="K126" s="4"/>
+      <c r="L126" s="4"/>
+      <c r="M126" s="4"/>
+      <c r="N126" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="1">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="C127" s="4"/>
+      <c r="D127" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E127" s="4"/>
+      <c r="F127" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G127" s="4"/>
+      <c r="H127" s="4"/>
+      <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
+      <c r="K127" s="4"/>
+      <c r="L127" s="4"/>
+      <c r="M127" s="4"/>
+      <c r="N127" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="1">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="C128" s="4"/>
+      <c r="D128" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E128" s="4"/>
+      <c r="F128" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G128" s="4"/>
+      <c r="H128" s="4"/>
+      <c r="I128" s="4"/>
+      <c r="J128" s="4"/>
+      <c r="K128" s="4"/>
+      <c r="L128" s="4"/>
+      <c r="M128" s="4"/>
+      <c r="N128" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="1">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C129" s="4"/>
+      <c r="D129" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G129" s="4"/>
+      <c r="H129" s="4"/>
+      <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="1">
+        <v>129</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="C130" s="4"/>
+      <c r="D130" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E130" s="4"/>
+      <c r="F130" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+      <c r="I130" s="4"/>
+      <c r="J130" s="4"/>
+      <c r="K130" s="4"/>
+      <c r="L130" s="4"/>
+      <c r="M130" s="4"/>
+      <c r="N130" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="1">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C131" s="4"/>
+      <c r="D131" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="E131" s="4"/>
+      <c r="F131" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G131" s="4"/>
+      <c r="H131" s="4"/>
+      <c r="I131" s="4"/>
+      <c r="J131" s="4"/>
+      <c r="K131" s="4"/>
+      <c r="L131" s="4"/>
+      <c r="M131" s="4"/>
+      <c r="N131" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C132" s="4"/>
+      <c r="D132" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E132" s="4"/>
+      <c r="F132" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G132" s="4"/>
+      <c r="H132" s="4"/>
+      <c r="I132" s="4"/>
+      <c r="J132" s="4"/>
+      <c r="K132" s="4"/>
+      <c r="L132" s="4"/>
+      <c r="M132" s="4"/>
+      <c r="N132" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C133" s="4"/>
+      <c r="D133" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+      <c r="L133" s="4"/>
+      <c r="M133" s="4"/>
+      <c r="N133" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C134" s="4"/>
+      <c r="D134" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E134" s="4"/>
+      <c r="F134" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G134" s="4"/>
+      <c r="H134" s="4"/>
+      <c r="I134" s="4"/>
+      <c r="J134" s="4"/>
+      <c r="K134" s="4"/>
+      <c r="L134" s="4"/>
+      <c r="M134" s="4"/>
+      <c r="N134" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C135" s="4"/>
+      <c r="D135" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
+      <c r="I135" s="4"/>
+      <c r="J135" s="4"/>
+      <c r="K135" s="4"/>
+      <c r="L135" s="4"/>
+      <c r="M135" s="4"/>
+      <c r="N135" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="C136" s="4"/>
+      <c r="D136" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E136" s="4"/>
+      <c r="F136" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G136" s="4"/>
+      <c r="H136" s="4"/>
+      <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
+      <c r="K136" s="4"/>
+      <c r="L136" s="4"/>
+      <c r="M136" s="4"/>
+      <c r="N136" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C137" s="4"/>
+      <c r="D137" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E137" s="4"/>
+      <c r="F137" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G137" s="4"/>
+      <c r="H137" s="4"/>
+      <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
+      <c r="K137" s="4"/>
+      <c r="L137" s="4"/>
+      <c r="M137" s="4"/>
+      <c r="N137" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C138" s="4"/>
+      <c r="D138" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E138" s="4"/>
+      <c r="F138" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G138" s="4"/>
+      <c r="H138" s="4"/>
+      <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+      <c r="L138" s="4"/>
+      <c r="M138" s="4"/>
+      <c r="N138" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C139" s="4"/>
+      <c r="D139" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
+      <c r="I139" s="4"/>
+      <c r="J139" s="4"/>
+      <c r="K139" s="4"/>
+      <c r="L139" s="4"/>
+      <c r="M139" s="4"/>
+      <c r="N139" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C140" s="4"/>
+      <c r="D140" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E140" s="4"/>
+      <c r="F140" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G140" s="4"/>
+      <c r="H140" s="4"/>
+      <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
+      <c r="K140" s="4"/>
+      <c r="L140" s="4"/>
+      <c r="M140" s="4"/>
+      <c r="N140" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C141" s="4"/>
+      <c r="D141" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E141" s="4"/>
+      <c r="F141" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G141" s="4"/>
+      <c r="H141" s="4"/>
+      <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
+      <c r="K141" s="4"/>
+      <c r="L141" s="4"/>
+      <c r="M141" s="4"/>
+      <c r="N141" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="1">
+        <v>141</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+      <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
+      <c r="K142" s="4"/>
+      <c r="L142" s="4"/>
+      <c r="M142" s="4"/>
+      <c r="N142" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="1">
+        <v>142</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C143" s="4"/>
+      <c r="D143" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E143" s="4"/>
+      <c r="F143" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G143" s="4"/>
+      <c r="H143" s="4"/>
+      <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
+      <c r="K143" s="4"/>
+      <c r="L143" s="4"/>
+      <c r="M143" s="4"/>
+      <c r="N143" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="1">
+        <v>143</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C144" s="4"/>
+      <c r="D144" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G144" s="4"/>
+      <c r="H144" s="4"/>
+      <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
+      <c r="K144" s="4"/>
+      <c r="L144" s="4"/>
+      <c r="M144" s="4"/>
+      <c r="N144" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="1">
+        <v>144</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C145" s="4"/>
+      <c r="D145" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E145" s="4"/>
+      <c r="F145" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G145" s="4"/>
+      <c r="H145" s="4"/>
+      <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
+      <c r="K145" s="4"/>
+      <c r="L145" s="4"/>
+      <c r="M145" s="4"/>
+      <c r="N145" s="4"/>
+    </row>
+    <row r="146" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="1">
+        <v>145</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C146" s="4"/>
+      <c r="D146" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
+      <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
+      <c r="K146" s="4"/>
+      <c r="L146" s="4"/>
+      <c r="M146" s="4"/>
+      <c r="N146" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="1">
+        <v>146</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C147" s="4"/>
+      <c r="D147" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="E147" s="4"/>
+      <c r="F147" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G147" s="4"/>
+      <c r="H147" s="4"/>
+      <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
+      <c r="K147" s="4"/>
+      <c r="L147" s="4"/>
+      <c r="M147" s="4"/>
+      <c r="N147" s="4"/>
+    </row>
+    <row r="148" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D79:D87 D47:D77 D89:D94">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D78">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D78">
+  <conditionalFormatting sqref="D2:D46">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D46">
+  <conditionalFormatting sqref="D95:D147">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/조사1.xlsx
+++ b/조사1.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="320">
   <si>
     <t>조사자</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -28,525 +28,6 @@
     <t>시설명</t>
   </si>
   <si>
-    <t>광주시립정신병원</t>
-  </si>
-  <si>
-    <t>주차장(전용2, 완속2)</t>
-  </si>
-  <si>
-    <t>국립야생동물질병관리원</t>
-  </si>
-  <si>
-    <t>청사주차장(전용1, 급속1, 완속1)</t>
-  </si>
-  <si>
-    <t>광주친환경자동차인증센터(친환경자동차부품인증센터)</t>
-  </si>
-  <si>
-    <t>주차장(급속1)</t>
-  </si>
-  <si>
-    <t>송정역 한국아델리움 더 씨티</t>
-  </si>
-  <si>
-    <t>지하 (전용2 충전2) A104구역, 지하 (전용1 충전1) B106구역 (급속)</t>
-  </si>
-  <si>
-    <t>케이티송정빌딩</t>
-  </si>
-  <si>
-    <t>지상 2대</t>
-  </si>
-  <si>
-    <t>SK텔레콤 송정사옥</t>
-  </si>
-  <si>
-    <t>지상 1대</t>
-  </si>
-  <si>
-    <t>효정요양병원</t>
-  </si>
-  <si>
-    <t>신관뒤 주차장(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>송정서초등학교</t>
-  </si>
-  <si>
-    <t>지상 1대 완속</t>
-  </si>
-  <si>
-    <t>송정중학교</t>
-  </si>
-  <si>
-    <t>지상 운동장옆 1대</t>
-  </si>
-  <si>
-    <t>광주소프트웨어마이스터고등학교</t>
-  </si>
-  <si>
-    <t>학교 주차장 입구쪽 1대</t>
-  </si>
-  <si>
-    <t>빛그린산학융합캠퍼스</t>
-  </si>
-  <si>
-    <t>연구관 앞 주차장(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>송정금강아파트</t>
-  </si>
-  <si>
-    <t>관리사무소 옆(전용7/충전7), 지하주차장 우측끝(전용2/충전2)</t>
-  </si>
-  <si>
-    <t>송정우방아이유쉘</t>
-  </si>
-  <si>
-    <t>204동 앞 1-2라인 앞(전용6, 완속6), 210동 앞 3-4라인 앞(전용9, 완속9)</t>
-  </si>
-  <si>
-    <t>대화아파트</t>
-  </si>
-  <si>
-    <t>103동 후면 : 전용5/충전5</t>
-  </si>
-  <si>
-    <t>송정역숲안애2차</t>
-  </si>
-  <si>
-    <t>201동앞: 전용4/충전4</t>
-  </si>
-  <si>
-    <t>광산엘리체레이크시티오피스텔</t>
-  </si>
-  <si>
-    <t>104동 앞 : 전용5/충전5 (급속1, 완속4), 102동 앞 : 전용11/충전11</t>
-  </si>
-  <si>
-    <t>도산호반1차</t>
-  </si>
-  <si>
-    <t>101동 옆 후문(전용5, 완속5)</t>
-  </si>
-  <si>
-    <t>도산호반2차</t>
-  </si>
-  <si>
-    <t>203동 5-6라인앞(전용3, 병행4, 완속7), 203동 7-8라인앞(병행3, 완속3)</t>
-  </si>
-  <si>
-    <t>온세계아파트</t>
-  </si>
-  <si>
-    <t>104동 앞 : 전용4/충전4, 지하2주차장:전용5/충전5, 102동 앞 : 전용8/충전8</t>
-  </si>
-  <si>
-    <t>명지 2차&lt;송정명지2차&gt;</t>
-  </si>
-  <si>
-    <t>201동앞 지상1층 전용5/충전5, 206동앞 지상1층 전용4/충전4</t>
-  </si>
-  <si>
-    <t>도산 우방아이유쉘</t>
-  </si>
-  <si>
-    <t>104동 3-4라인 앞(전용4, 완속4), 107동 1-2라인 앞(전용5, 완속5)</t>
-  </si>
-  <si>
-    <t>송정역 모아엘가</t>
-  </si>
-  <si>
-    <t>① 지상 (전용3 충전3) 106동 앞 (병행2), ② 지상 (전용3 충전3) 107동 앞 (병행2), ③ 지상 (전용3 충전3) 104동 앞 (병행2), ④ 지상 (전용6 충전6) 102동 뒤 (병행4), ⑤ 지상 (전용3 충전3) 101동 앞 (병행2), ⑥ 지하 (전용2 충전2) 101동 12라인 앞, ⑦ 지하 (전용1 충전1) 101동 12라인 앞</t>
-  </si>
-  <si>
-    <t>상아</t>
-  </si>
-  <si>
-    <t>지상(전용3 충전3) 101동 앞</t>
-  </si>
-  <si>
-    <t>호반청암빌라트</t>
-  </si>
-  <si>
-    <t>무등파크</t>
-  </si>
-  <si>
-    <t>지하주차장 53-54구역(전용1, 병행1, 완속2)</t>
-  </si>
-  <si>
-    <t>삼라미주</t>
-  </si>
-  <si>
-    <t>지상 주차장 전용5, 충전2</t>
-  </si>
-  <si>
-    <t>대덕9차</t>
-  </si>
-  <si>
-    <t>901동 후면 : 전용7/충전7</t>
-  </si>
-  <si>
-    <t>송정라인1차</t>
-  </si>
-  <si>
-    <t>정문경비실 입구 : 전용5/충전5</t>
-  </si>
-  <si>
-    <t>카이스트빌1</t>
-  </si>
-  <si>
-    <t>지상1층 주차장 전용9/충전4</t>
-  </si>
-  <si>
-    <t>카이스트빌2</t>
-  </si>
-  <si>
-    <t>201동 3-4라인앞(전용2, 병행1, 완속3), 202동 1-2라인앞(전용1, 병행1, 완속2)</t>
-  </si>
-  <si>
-    <t>도산대주2차</t>
-  </si>
-  <si>
-    <t>201동 3-5라인 앞(전용3, 병행1, 완속4)</t>
-  </si>
-  <si>
-    <t>금강2차</t>
-  </si>
-  <si>
-    <t>지상1층 주차장 전용7/충전3</t>
-  </si>
-  <si>
-    <t>해피드림</t>
-  </si>
-  <si>
-    <t>101동 앞 (전용2, 완속2)</t>
-  </si>
-  <si>
-    <t>명지</t>
-  </si>
-  <si>
-    <t>102동 앞: 전용4/충전4</t>
-  </si>
-  <si>
-    <t>신한화</t>
-  </si>
-  <si>
-    <t>지상1층 주차장 전용2/충전2</t>
-  </si>
-  <si>
-    <t>삼라극동</t>
-  </si>
-  <si>
-    <t>서경</t>
-  </si>
-  <si>
-    <t>101동 1-2라인 뒷편(전용2, 병행1, 완속3), 102동 10-11라인 앞(전용1, 병행1, 완속2)</t>
-  </si>
-  <si>
-    <t>극동마이다스</t>
-  </si>
-  <si>
-    <t>지상 (전용 3 충전 3) 아파트입구</t>
-  </si>
-  <si>
-    <t>광신프로그레스</t>
-  </si>
-  <si>
-    <t>지상 (전용 4 충전 4) 102동앞, 지하 (전용 2 충전 2) 101동 (병행2), 지하 (전용 2 충전 2) 102동 (병행2)</t>
-  </si>
-  <si>
-    <t>송정매일시장 주차타워</t>
-  </si>
-  <si>
-    <t>지상3층 A지역: 전용1/충전1(급1), 지상3층 B지역: 전용3/충전3(급3)</t>
-  </si>
-  <si>
-    <t>1913송정역시장 주차타워</t>
-  </si>
-  <si>
-    <t>1층 좌측 : 전용 1, 2층 중앙 : 전용 1, 2층 좌측 : 전용 2 / 충전2, 3층 중앙 : 전용 1, 4층 중앙 : 전용 1</t>
-  </si>
-  <si>
-    <t>광산CC 주차장</t>
-  </si>
-  <si>
-    <t>출입구 좌측 : 전용2/충전2(급2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광주송정역뒤 공영주차장 </t>
-  </si>
-  <si>
-    <t>출입구 좌측: 전용3/충전1(급1)</t>
-  </si>
-  <si>
-    <t>광산구청사 주차장</t>
-  </si>
-  <si>
-    <t>지하1층 D-7 구역: 전용4 / 충전1(급속), 지하2층 A-6 구역: 전용2 / 충전2(완속)</t>
-  </si>
-  <si>
-    <t>차고지(광산구생활환경종합센터)</t>
-  </si>
-  <si>
-    <t>한국도로교통공단 광주교통방송</t>
-  </si>
-  <si>
-    <t>주차장 (전용2, 급속2), (전용2, 완속2)</t>
-  </si>
-  <si>
-    <t>광주국토관리사무소</t>
-  </si>
-  <si>
-    <t>정문 옆(차고동)(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>광주우편집중국</t>
-  </si>
-  <si>
-    <t>지상1층 전용10/충전4 (급속1, 완속3)</t>
-  </si>
-  <si>
-    <t>보이저 첨단</t>
-  </si>
-  <si>
-    <t>4층 엘리베이터 앞쪽(전용2, 급속2), 6층 테슬라 전용(전용6, 급속6)</t>
-  </si>
-  <si>
-    <t>첨단트레비엔 H-CITY</t>
-  </si>
-  <si>
-    <t>지하2층 03구역(전용1, 급속1(2)), 04구역(전용1, 급속1(3)), 지하2층 상가엘리베이터 입구(전용1, 급속1(3))</t>
-  </si>
-  <si>
-    <t>CMC TOWER&lt;신축유의!&gt;</t>
-  </si>
-  <si>
-    <t>지상4층 A구역(전용4, 완속4), B구역(전용3, 완속3), 지상3층 A구역(전용1, 급속1), B구역(전용4, 완속4), 지상2층 A구역(전용2, 완속2), C구역(전용3, 완속3), 지상2층 B구역(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>야스텍타워</t>
-  </si>
-  <si>
-    <t>지하1층 엘리베이터 앞(전용2, 완속2)</t>
-  </si>
-  <si>
-    <t>쌍암힐스테이트리버파크(오피스텔)</t>
-  </si>
-  <si>
-    <t>지하1층 J09구역(전용2, 완속2), 지하2층 J09구역(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">더 시너지 첨단 </t>
-  </si>
-  <si>
-    <t>지하2층 엘리베이터 앞(전용3, 급속1, 완속2)</t>
-  </si>
-  <si>
-    <t>아크레타 첨단</t>
-  </si>
-  <si>
-    <t>씨네파크(키넥스9시네마)</t>
-  </si>
-  <si>
-    <t>쌍암동 미르채 리버파크 오피스텔</t>
-  </si>
-  <si>
-    <t>지하2층 출구쪽(전용2, 급속1, 완속1), 지하3층 출구쪽(전용2, 완속2)</t>
-  </si>
-  <si>
-    <t>첨단 뉴타운 한국아델리움</t>
-  </si>
-  <si>
-    <t>지하1층 2대 (전용2/충전2) 급속1 완속1, 지하2층 1대 (전용1/충전1)</t>
-  </si>
-  <si>
-    <t>첨단 한국아델리움 메트로시티</t>
-  </si>
-  <si>
-    <t>지하4층 1대 (전용1/충전1)급속, 지하3층 1대 (전용1/충전1), 지하2층 1대 (전용1/충전1)</t>
-  </si>
-  <si>
-    <t>첨단센츄럴빌딩</t>
-  </si>
-  <si>
-    <t>지상4층 주차장(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>첨단중해마루힐 주차타워</t>
-  </si>
-  <si>
-    <t>월계동 주차빌딩(광주첨단점 아이파킹주차장)</t>
-  </si>
-  <si>
-    <t>센트럴파크 첨단주차장</t>
-  </si>
-  <si>
-    <t>힐스테이트 첨단 힐스에비뉴</t>
-  </si>
-  <si>
-    <t>지하1층01구역(전용1, 급속1), 지하1층02구역(전용5, 완속5)</t>
-  </si>
-  <si>
-    <t>첨단 LC타워</t>
-  </si>
-  <si>
-    <t>지하주차장(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>대상파크타운</t>
-  </si>
-  <si>
-    <t>지하주차장 출구쪽(전용4, 완속4)</t>
-  </si>
-  <si>
-    <t>폭스존(메가박스 첨단 건물)</t>
-  </si>
-  <si>
-    <t>쌍암동 첨단프라자</t>
-  </si>
-  <si>
-    <t>지하1층(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>애플타워</t>
-  </si>
-  <si>
-    <t>롯데마트 첨단점</t>
-  </si>
-  <si>
-    <t>주차장 2층 A(전용3, 급속1(3개)), 주차장 2층 B(전용8, 완속6(8개)), 주차장 2층 C(전용1, 급속2(4개))</t>
-  </si>
-  <si>
-    <t>KT 첨단빌딩</t>
-  </si>
-  <si>
-    <t>지상1층 고객주차장(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>광주노블스테이호텔</t>
-  </si>
-  <si>
-    <t>지상1층 출구쪽(전용1, 완속1)</t>
-  </si>
-  <si>
-    <t>cgv 주차타워</t>
-  </si>
-  <si>
-    <t>첨단종합병원</t>
-  </si>
-  <si>
-    <t>원내주차장 1층(전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>골드타워</t>
-  </si>
-  <si>
-    <t>겨자씨교회</t>
-  </si>
-  <si>
-    <t>다담식자재마트</t>
-  </si>
-  <si>
-    <t>지상4층 4A구역(전용4, 급속1, 완속3)</t>
-  </si>
-  <si>
-    <t>쌍암힐스테이트리버파크</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;지하1층&gt;101동 E07 2대, 102동 C19 2대, 105동 V09 2대 &lt;지하2층&gt;105동 T12 3대, 105동 T10 2대, 105동 T09 1대, 101동 E13 2대, D13 2대, 101동 C13·14·15 콘센트형 3대, 101동 B2 2대, 102동 C21 2대, 105동 O12 콘센트형 2대 &lt;지하3층&gt;109동 B3 2대, 109동 B3 2대, 105동 U11 2대 </t>
-  </si>
-  <si>
-    <t>첨단대라수어썸시티5차</t>
-  </si>
-  <si>
-    <t>3층 주차장 J9-L9 (병행5, 완속5), 4층 주차장 M10-L11 (전용3, 완속3), 3층 주차장 J7-J8 (병행7, 완속7), 4층 주차장 J8-J9 (전용3, 완속3), 3층 주차장 K6-N6 (병행7, 완속7), 4층 주차장 H2-I2 (전용3, 완속3), 4층 주차장 L4-L5 (전용2, 완속2), 4층 주차장 B4구역 (전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>첨단중해마루힐</t>
-  </si>
-  <si>
-    <t>102동 2층 3,4라인앞 (전용9, 완속9)</t>
-  </si>
-  <si>
-    <t>첨단에이엠시티 센트럴파크2차</t>
-  </si>
-  <si>
-    <t>201동 주차장(전용2, 완속2), 202동 주차장(전용2, 완속2)</t>
-  </si>
-  <si>
-    <t>첨단대라수1차</t>
-  </si>
-  <si>
-    <t>103동 지하1층 37,38구역 (전용2, 완속2), 102동 지하1층 41,42구역 (전용2, 완속2), 104동 지하1층 05,06구역 (전용2, 완속2), 101동 지하1층 01~03구역 (전용3, 완속3), 104동 2층 주차장 30~34구역 (병행3, 완속3), 103동 2층 주차장 25~26구역 (병행3, 완속3)</t>
-  </si>
-  <si>
-    <t>쌍암중흥s클래스리버시티</t>
-  </si>
-  <si>
-    <t>지하2층 104동 B03구역 (전용2, 병행4, 완속6), 103동 B01구역 (전용2, 병행4, 완속6), 102동 A17구역 (전용3, 급속1, 완속2), 101동 A01구역 (전용2, 병행4, 완속6), 101동 A03구역 (전용2, 병행4, 완속6)</t>
-  </si>
-  <si>
-    <t>첨단에이엠시티 센트럴파크1차</t>
-  </si>
-  <si>
-    <t>101동앞 2대 지상</t>
-  </si>
-  <si>
-    <t>첨단 중해마루힐 2차</t>
-  </si>
-  <si>
-    <t>203동 지하2층 출입구 (전용3, 급속1, 완속2), 203동 지하1층 출입구 (전용3, 급속1, 완속2), 203동 지상2층 출입구 (전용3, 급속1, 완속2)</t>
-  </si>
-  <si>
-    <t>쌍암동 대라수 주상복합 3차</t>
-  </si>
-  <si>
-    <t>지하1층 301동 1~2라인앞(B1~J1)(전용2, 병행7, 완속9), 지하3층 302동 1~2라인앞(병행5, 완속5), 지상2층 303동 3~4라인앞(병행5, 완속5)</t>
-  </si>
-  <si>
-    <t>힐스테이트첨단</t>
-  </si>
-  <si>
-    <t>지하4층 102동 출입구 옆 A(전용4, 완속3), 지하4층 102동 출입구 옆 B(전용2, 급속1), 지하4층 102동 출입구 옆 C(전용4, 완속2)</t>
-  </si>
-  <si>
-    <t>무들에코클래스</t>
-  </si>
-  <si>
-    <t>지상1층 (전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>쌍암동 대라수 주상복합 2차</t>
-  </si>
-  <si>
-    <t>201동 지상1층 01구역 (병행1, 완속1), 201동 지상1층 1~2라인 (병행1, 완속1), 201동 지상1층 10구역 (병행1, 완속1), 201동 지하1층 03구역 (전용2, 완속2), 201동 지상2층 04구역 (전용3, 완속3), 201동 지상3층 03구역 (병행3, 완속3)</t>
-  </si>
-  <si>
-    <t>첨단 LH3단지(행복주택)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3층 05 (전용2/급속 1), 1층 07 (전용4/완속1), </t>
-  </si>
-  <si>
-    <t>첨단 LH2단지(행복주택)</t>
-  </si>
-  <si>
-    <t>지상2층 계단실 옆(전용1, 완속1)</t>
-  </si>
-  <si>
-    <t>일신프레뷰</t>
-  </si>
-  <si>
-    <t>지상5층 (전용3, 완속3)</t>
-  </si>
-  <si>
-    <t>첨단 LH1단지(행복주택)</t>
-  </si>
-  <si>
-    <t>지상2층 05구역(전용1, 완속1)</t>
-  </si>
-  <si>
     <t>연번</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -559,771 +40,961 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>실태조사완료여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상세위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>운영기관</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전기타입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전용량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농협하나로유통(수완)</t>
+  </si>
+  <si>
+    <t>수완센트럴병원</t>
+  </si>
+  <si>
+    <t>샤브올데이</t>
+  </si>
+  <si>
+    <t>더블유여성병원</t>
+  </si>
+  <si>
+    <t>KS병원</t>
+  </si>
+  <si>
+    <t>수완에너지주식회사</t>
+  </si>
+  <si>
+    <t>수완GS자이</t>
+  </si>
+  <si>
+    <t>수완코오롱하늘채</t>
+  </si>
+  <si>
+    <t>신안실크밸리</t>
+  </si>
+  <si>
+    <t>수완휴먼시아5단지</t>
+  </si>
+  <si>
+    <t>수완이지더원</t>
+  </si>
+  <si>
+    <t>수완 우미린2차</t>
+  </si>
+  <si>
+    <t>모아엘가 수완</t>
+  </si>
+  <si>
+    <t>수완2차중흥</t>
+  </si>
+  <si>
+    <t>수완휴먼시아 4단지</t>
+  </si>
+  <si>
+    <t>수완휴먼시아 6단지</t>
+  </si>
+  <si>
+    <t>진흥더루벤스</t>
+  </si>
+  <si>
+    <t>수완휴먼시아 1단지</t>
+  </si>
+  <si>
+    <t>수완1차 중흥</t>
+  </si>
+  <si>
+    <t>수완 대방노블랜드</t>
+  </si>
+  <si>
+    <t>수완 호반베르디움 2차</t>
+  </si>
+  <si>
+    <t>수완문화체육센터(체육진흥과-지상)</t>
+  </si>
+  <si>
+    <t>수완문화체육센터(교통지도과-지하/체육과-지상)</t>
+  </si>
+  <si>
+    <t>광주 명진고등학교</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 261</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로 6</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로 160</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 331</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로 220</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로 130</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로95번길 45</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로137번길 39</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로330번길 34</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로145번길 42</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로101번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로330번길 16</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로132번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로381번길 27</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로145번길 15</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로145번길 43</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로329번길 51</t>
+  </si>
+  <si>
+    <t>광주 광산구 장덕로6번길 35</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로123번길 70</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로76번길 74</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로76번길 40</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영로329번길 19</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로132번길 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 수완로12번길 21</t>
+  </si>
+  <si>
+    <t>정은진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국방송통신대학교 광주전남지역학습관</t>
+  </si>
+  <si>
+    <t>남부대학교</t>
+  </si>
+  <si>
+    <t>태호 골프연습장</t>
+  </si>
+  <si>
+    <t>명성골프장</t>
+  </si>
+  <si>
+    <t>삼라주차빌딩</t>
+  </si>
+  <si>
+    <t>월계초등학교</t>
+  </si>
+  <si>
+    <t>첨단중학교</t>
+  </si>
+  <si>
+    <t>전자공업고등학교</t>
+  </si>
+  <si>
+    <t>첨단금호타운</t>
+  </si>
+  <si>
+    <t>첨단동부아파트</t>
+  </si>
+  <si>
+    <t>첨단동아아파트</t>
+  </si>
+  <si>
+    <t>첨단 성원아파트</t>
+  </si>
+  <si>
+    <t>첨단신동아</t>
+  </si>
+  <si>
+    <t>첨단부영3차</t>
+  </si>
+  <si>
+    <t>첨단부영1차</t>
+  </si>
+  <si>
+    <t>첨단모아미래도</t>
+  </si>
+  <si>
+    <t>첨단대우1차</t>
+  </si>
+  <si>
+    <t>첨단라인5차</t>
+  </si>
+  <si>
+    <t>첨단삼능1차</t>
+  </si>
+  <si>
+    <t>첨단라인7차</t>
+  </si>
+  <si>
+    <t>첨단부영2차</t>
+  </si>
+  <si>
+    <t>첨단건영 1차</t>
+  </si>
+  <si>
+    <t>첨단두산2차</t>
+  </si>
+  <si>
+    <t>첨단호반1차</t>
+  </si>
+  <si>
+    <t>첨단일신</t>
+  </si>
+  <si>
+    <t>첨단모아</t>
+  </si>
+  <si>
+    <t>첨단금광</t>
+  </si>
+  <si>
+    <t>첨단호반2차</t>
+  </si>
+  <si>
+    <t>첨단서라</t>
+  </si>
+  <si>
+    <t>첨단벽산</t>
+  </si>
+  <si>
+    <t>첨단우미3차</t>
+  </si>
+  <si>
+    <t>첨단우미2차</t>
+  </si>
+  <si>
+    <t>첨단라인8차</t>
+  </si>
+  <si>
+    <t>첨단리젠시빌 3-5</t>
+  </si>
+  <si>
+    <t>첨단부영e그린 1차</t>
+  </si>
+  <si>
+    <t>첨단부영6차</t>
+  </si>
+  <si>
+    <t>첨단부영7차</t>
+  </si>
+  <si>
+    <t>금호더어울림 더 테라스</t>
+  </si>
+  <si>
+    <t>첨단기산</t>
+  </si>
+  <si>
+    <t>첨단대주</t>
+  </si>
+  <si>
+    <t>첨단삼성</t>
+  </si>
+  <si>
+    <t>첨단쌍용</t>
+  </si>
+  <si>
+    <t>첨단라인3차</t>
+  </si>
+  <si>
+    <t>첨단라인2차</t>
+  </si>
+  <si>
+    <t>첨단우미1차</t>
+  </si>
+  <si>
+    <t>첨단라인6차</t>
+  </si>
+  <si>
+    <t>이승수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>노기섭</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이승수</t>
+    <t>광주 광산구 첨단내촌로 6</t>
+  </si>
+  <si>
+    <t>광주 광산구 남부대길 1</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단과기로 79-37</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단과기로 83</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 5</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단내촌로 83</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단내촌로 16</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로 7</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 42-5</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로 201</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 7</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 92</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 88-22</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로68번길 131</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 170</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 77</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 88-21</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 88-16</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 727-19</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 673-5</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로68번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 104</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 117-22</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 117-35</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 42-14</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 6</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 42-4</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 59</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단내촌로 102</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 16</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단내촌로 93</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 673-13</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단내촌로 101</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로68번길 99</t>
+  </si>
+  <si>
+    <t>광주 광산구 산월로 81</t>
+  </si>
+  <si>
+    <t>광주 광산구 산월로 64</t>
+  </si>
+  <si>
+    <t>광주 광산구 산월로 80</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단과기로 91-23</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 727-6</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로 153</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 743</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 21</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 727-5</t>
+  </si>
+  <si>
+    <t>광주 광산구 월계로 109</t>
+  </si>
+  <si>
+    <t>광주 광산구 첨단중앙로181번길 65</t>
+  </si>
+  <si>
+    <t>광주 광산구 임방울대로 673-21</t>
+  </si>
+  <si>
+    <t>광주광산경찰서</t>
+  </si>
+  <si>
+    <t>광주광역시지방경찰청</t>
+  </si>
+  <si>
+    <t>광주광역시인재교육원</t>
+  </si>
+  <si>
+    <t>광주광역시 소방학교</t>
+  </si>
+  <si>
+    <t>광주에스타워</t>
+  </si>
+  <si>
+    <t>해룡유통 소촌점</t>
+  </si>
+  <si>
+    <t>대한상공회의소 광주인력개발원</t>
+  </si>
+  <si>
+    <t>호남대학교</t>
+  </si>
+  <si>
+    <t>소촌그린힐스골프클럽</t>
+  </si>
+  <si>
+    <t>(주)구시월드</t>
+  </si>
+  <si>
+    <t>광주문화체육센터</t>
+  </si>
+  <si>
+    <t>송정동초등학교</t>
+  </si>
+  <si>
+    <t>선운초등학교</t>
+  </si>
+  <si>
+    <t>보문고등학교</t>
+  </si>
+  <si>
+    <t>광주자동화설비마이스터고등학교</t>
+  </si>
+  <si>
+    <t>선예학교</t>
+  </si>
+  <si>
+    <t>소촌라인1차</t>
+  </si>
+  <si>
+    <t>송광파크맨션2차</t>
+  </si>
+  <si>
+    <t>선운이지더원2단지</t>
+  </si>
+  <si>
+    <t>소촌동 모아드림1차</t>
+  </si>
+  <si>
+    <t>소촌대성베르힐</t>
+  </si>
+  <si>
+    <t>소촌서라1차</t>
+  </si>
+  <si>
+    <t>희망타운2단지</t>
+  </si>
+  <si>
+    <t>선운2레니체</t>
+  </si>
+  <si>
+    <t>소촌 모아엘가</t>
+  </si>
+  <si>
+    <t>소촌라인2차</t>
+  </si>
+  <si>
+    <t>스위트밸리3차</t>
+  </si>
+  <si>
+    <t>신촌 대주</t>
+  </si>
+  <si>
+    <t>선운 모아엘가</t>
+  </si>
+  <si>
+    <t>선운지구 휴먼시아</t>
+  </si>
+  <si>
+    <t>선운 해광샹그릴라</t>
+  </si>
+  <si>
+    <t>소촌2차 국제미소래</t>
+  </si>
+  <si>
+    <t>선운 더브이 레브리티</t>
+  </si>
+  <si>
+    <t>대덕무지개아파트</t>
+  </si>
+  <si>
+    <t>금호훼밀리파크</t>
+  </si>
+  <si>
+    <t>송광3차</t>
+  </si>
+  <si>
+    <t>소촌서라2차</t>
+  </si>
+  <si>
+    <t>가천</t>
+  </si>
+  <si>
+    <t>소촌서라3차</t>
+  </si>
+  <si>
+    <t>온세계</t>
+  </si>
+  <si>
+    <t>성화파인빌</t>
+  </si>
+  <si>
+    <t>중도다이아빌</t>
+  </si>
+  <si>
+    <t>선운2포리에</t>
+  </si>
+  <si>
+    <t>소촌스위트벨리 1차</t>
+  </si>
+  <si>
+    <t>소촌스위트벨리 2차</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로 551</t>
+  </si>
+  <si>
+    <t>광주 광산구 용아로 112</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 53-27</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 53-84</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로 455</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 30</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 37</t>
+  </si>
+  <si>
+    <t>광주 광산구 호남대길 90</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로149번길 20-26</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운로20번길 53</t>
+  </si>
+  <si>
+    <t>광주 광산구 사암로 46</t>
+  </si>
+  <si>
+    <t>광주 광산구 사암로27번길 58</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운중앙로 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로529번길 37</t>
+  </si>
+  <si>
+    <t>광주 광산구 사암로92번길 136-26</t>
+  </si>
+  <si>
+    <t>광주 광산구 선암1로 7</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 38</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로647번길 32</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운중앙로 43</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로86번길 17</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로86번길 20-17</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로665번길 27</t>
+  </si>
+  <si>
+    <t>광주 광산구 선암로 19</t>
+  </si>
+  <si>
+    <t>광주 광산구 선암1로 43</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로 100</t>
+  </si>
+  <si>
+    <t>광주 광산구 금봉로 18</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 11</t>
+  </si>
+  <si>
+    <t>광주 광산구 사암로 24</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운중앙로 45</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운중앙로 68</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운로 17</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로42번길 163</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로449번길 23</t>
+  </si>
+  <si>
+    <t>광주 광산구 금봉로 36</t>
+  </si>
+  <si>
+    <t>광주 광산구 사암로95번길 42</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로653번길 20</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로665번길 26</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로595번길 13</t>
+  </si>
+  <si>
+    <t>광주 광산구 어등대로653번길 89</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 20</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 53-17</t>
+  </si>
+  <si>
+    <t>광주 광산구 사암로 72-10</t>
+  </si>
+  <si>
+    <t>광주 광산구 선운중앙로 89</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 10</t>
+  </si>
+  <si>
+    <t>광주 광산구 소촌로152번길 5</t>
+  </si>
+  <si>
+    <t>신창동 마한유적 체험관</t>
+  </si>
+  <si>
+    <t>광주교육시민협치 진흥원</t>
+  </si>
+  <si>
+    <t>신창 프뤼몰타운</t>
+  </si>
+  <si>
+    <t>신창주차타워</t>
+  </si>
+  <si>
+    <t>한듬레포츠센터</t>
+  </si>
+  <si>
+    <t>주차장(SM마트 신창점)</t>
+  </si>
+  <si>
+    <t>마트앤매트 신가점</t>
+  </si>
+  <si>
+    <t>신가병원</t>
+  </si>
+  <si>
+    <t>산들요양병원</t>
+  </si>
+  <si>
+    <t>광주보건대학</t>
+  </si>
+  <si>
+    <t>해광가구</t>
+  </si>
+  <si>
+    <t>전남공업고등학교</t>
+  </si>
+  <si>
+    <t>운남진아리채리버힐스</t>
+  </si>
+  <si>
+    <t>수등리안</t>
+  </si>
+  <si>
+    <t>신창부영1차</t>
+  </si>
+  <si>
+    <t>신창5차 호반베르디움</t>
+  </si>
+  <si>
+    <t>신창3차부영</t>
+  </si>
+  <si>
+    <t>운남주공3단지</t>
+  </si>
+  <si>
+    <t>신창동대라수</t>
+  </si>
+  <si>
+    <t>신창 호반베르디움 3차</t>
+  </si>
+  <si>
+    <t>신창유탑유블레스리버뷰</t>
+  </si>
+  <si>
+    <t>운남주공1단지</t>
+  </si>
+  <si>
+    <t>운남주공2단지</t>
+  </si>
+  <si>
+    <t>신가호반리젠시빌1차</t>
+  </si>
+  <si>
+    <t>우미이노스빌</t>
+  </si>
+  <si>
+    <t>운남남양</t>
+  </si>
+  <si>
+    <t>신창삼능</t>
+  </si>
+  <si>
+    <t>신창 도시공사</t>
+  </si>
+  <si>
+    <t>신창부영5차</t>
+  </si>
+  <si>
+    <t>신창부영6차</t>
+  </si>
+  <si>
+    <t>신창 해광샹그릴라</t>
+  </si>
+  <si>
+    <t>신창2차남양휴튼</t>
+  </si>
+  <si>
+    <t>수완대라수어썸테라스</t>
+  </si>
+  <si>
+    <t>중흥1차(101동)</t>
+  </si>
+  <si>
+    <t>모아미래도</t>
+  </si>
+  <si>
+    <t>운남공용주차장</t>
+  </si>
+  <si>
+    <t>광주광산 한두레농산㈜</t>
+  </si>
+  <si>
+    <t>광주 광산구 북문대로 396-2</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로322번길 6</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로 64</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로72번길 10-29</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로 217</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로251번길 24</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로273번안길 12</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로 316</t>
+  </si>
+  <si>
+    <t>광주 광산구 풍영정길 227-1</t>
+  </si>
+  <si>
+    <t>광주 광산구 북문대로419번길 73</t>
+  </si>
+  <si>
+    <t>광주 광산구 하남대로 352</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로322번길 26</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로273번길 23</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로258번길 13</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로265번길 22</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로251번길 27</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로161번길 34</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로 307-11</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로 326</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로161번길 19</t>
+  </si>
+  <si>
+    <t>광주 광산구 장신로 306-37</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로273번길 76</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로 280</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로258번길 10</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로219번길 45</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로 20</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로252번길 46</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로71번길 16</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로35번길 20</t>
+  </si>
+  <si>
+    <t>광주 광산구 수등로258번길 46</t>
+  </si>
+  <si>
+    <t>광주 광산구 신창로71번길 17</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로252번길 10</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로382번길 114-1</t>
+  </si>
+  <si>
+    <t>광주 광산구 북문대로419번길 27-7</t>
+  </si>
+  <si>
+    <t>광주 광산구 목련로219번길 112</t>
+  </si>
+  <si>
+    <t>광주 광산구 왕버들로 207</t>
+  </si>
+  <si>
+    <t>수완양우내안애 1차</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실태조사완료여부</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>통합본</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상세위치</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>운영기관</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전기상태</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전기ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전기타입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>충전용량</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로182번길 40</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 22-16</t>
-  </si>
-  <si>
-    <t>광주 광산구 앰코로 11</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 19-20</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로106번길 25</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로152번길 81-15</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단강변로87번길 5</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 47</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로800번길 71</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 29-31</t>
-  </si>
-  <si>
-    <t>광주 광산구 월계로 235-8</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 60-3</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로 773</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로 136</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 22-57</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로116번길 31</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로106번길 65-3</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로 96</t>
-  </si>
-  <si>
-    <t>광주 광산구 월계로 203</t>
-  </si>
-  <si>
-    <t>광주 광산구 앰코로 35</t>
-  </si>
-  <si>
-    <t>광주 광산구 월계로 217</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 30</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단강변로99번길 22</t>
-  </si>
-  <si>
-    <t>광주 광산구 월계로 175</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 19-7</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 29-32</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로170번길 59</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로152번길 80</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단강변로 94</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 21-10</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단강변로 100</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로182번길 90</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 60-6</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로170번길 87</t>
-  </si>
-  <si>
-    <t>광주 광산구 앰코로 21</t>
-  </si>
-  <si>
-    <t>광주 광산구 월계로 223-8</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로182번길 50</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로182번길 76</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 22-77</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로182번길 8</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 60-5</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 22-54</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로800번길 11-5</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로825번길 9</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로826번길 22-22</t>
-  </si>
-  <si>
-    <t>광주 광산구 첨단중앙로152번길 6-8</t>
-  </si>
-  <si>
-    <t>광주 광산구 삼도로 84-3</t>
-  </si>
-  <si>
-    <t>광주 광산구 송암길 1</t>
-  </si>
-  <si>
-    <t>광주 광산구 빛동10로 23</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정로15번길 27</t>
-  </si>
-  <si>
-    <t>광주 광산구 상무대로 268</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로 308</t>
-  </si>
-  <si>
-    <t>광주 광산구 노안삼도로 1263</t>
-  </si>
-  <si>
-    <t>광주 광산구 상무대로 114</t>
-  </si>
-  <si>
-    <t>광주 광산구 내상로15번길 23</t>
-  </si>
-  <si>
-    <t>광주 광산구 상무대로 312</t>
-  </si>
-  <si>
-    <t>광주 광산구 빛그린산단로 365</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정로 77</t>
-  </si>
-  <si>
-    <t>광주 광산구 평동로1100번길 71</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로212번길 31-8</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정로85번길 10</t>
-  </si>
-  <si>
-    <t>광주 광산구 용동길63번길 31</t>
-  </si>
-  <si>
-    <t>광주 광산구 도산로9번길 35</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로162번길 11-6</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정로 80</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로320번길 16-15</t>
-  </si>
-  <si>
-    <t>광주 광산구 평동로1098번길 185</t>
-  </si>
-  <si>
-    <t>광주 광산구 평동로1101번길 40</t>
-  </si>
-  <si>
-    <t>광주 광산구 도산신송길 31</t>
-  </si>
-  <si>
-    <t>광주 광산구 도산로12번길 17-25</t>
-  </si>
-  <si>
-    <t>광주 광산구 도산로 3</t>
-  </si>
-  <si>
-    <t>광주 광산구 남동길 15</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정로65번길 28</t>
-  </si>
-  <si>
-    <t>광주 광산구 용보로27번길 46</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로182번길 15-11</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로181번길 30</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로182번길 16-3</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로182번길 15-12</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로212번길 54</t>
-  </si>
-  <si>
-    <t>광주 광산구 송도로320번길 11</t>
-  </si>
-  <si>
-    <t>광주 광산구 내상로 80</t>
-  </si>
-  <si>
-    <t>광주 광산구 남동길 18-10</t>
-  </si>
-  <si>
-    <t>광주 광산구 도산로 28</t>
-  </si>
-  <si>
-    <t>광주 광산구 평동로1119번길 25</t>
-  </si>
-  <si>
-    <t>광주 광산구 광산로20번길 28</t>
-  </si>
-  <si>
-    <t>광주 광산구 내상로 10</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정로 14</t>
-  </si>
-  <si>
-    <t>광주 광산구 오목내길 26</t>
-  </si>
-  <si>
-    <t>광주 광산구 송정동 1005-1</t>
-  </si>
-  <si>
-    <t>광주 광산구 광산로29번길 15</t>
-  </si>
-  <si>
-    <t>광주 광산구 연산로 280</t>
-  </si>
-  <si>
-    <t>지하1층 (전용3,완속3)</t>
-  </si>
-  <si>
-    <t>농협하나로유통(수완)</t>
-  </si>
-  <si>
-    <t>수영빌딩</t>
-  </si>
-  <si>
-    <t>성덕주차타워</t>
-  </si>
-  <si>
-    <t>수완센트럴병원</t>
-  </si>
-  <si>
-    <t>주차장</t>
-  </si>
-  <si>
-    <t>샤브올데이</t>
-  </si>
-  <si>
-    <t>애플타워주차장</t>
-  </si>
-  <si>
-    <t>더블유여성병원</t>
-  </si>
-  <si>
-    <t>세계로 365병원</t>
-  </si>
-  <si>
-    <t>남궁빌딩</t>
-  </si>
-  <si>
-    <t>국선빌딩</t>
-  </si>
-  <si>
-    <t>KS병원</t>
-  </si>
-  <si>
-    <t>BYC 광주수완빌딩</t>
-  </si>
-  <si>
-    <t>수완에너지주식회사</t>
-  </si>
-  <si>
-    <t>광주고실초등학교</t>
-  </si>
-  <si>
-    <t>새별초등학교</t>
-  </si>
-  <si>
-    <t>성덕중학교</t>
-  </si>
-  <si>
-    <t>장덕중학교</t>
-  </si>
-  <si>
-    <t>수완하나중학교</t>
-  </si>
-  <si>
-    <t>고실중학교</t>
-  </si>
-  <si>
-    <t>장덕고등학교</t>
-  </si>
-  <si>
-    <t>성덕고등학교</t>
-  </si>
-  <si>
-    <t>수완고등학교</t>
-  </si>
-  <si>
-    <t>수완대성베르힐</t>
-  </si>
-  <si>
-    <t>성덕마을새한포유</t>
-  </si>
-  <si>
-    <t>수완GS자이</t>
-  </si>
-  <si>
-    <t>신가2차호반리젠시빌</t>
-  </si>
-  <si>
-    <t>수완코오롱하늘채</t>
-  </si>
-  <si>
-    <t>신안실크밸리</t>
-  </si>
-  <si>
-    <t>수완휴먼시아5단지</t>
-  </si>
-  <si>
-    <t>수완이지더원</t>
-  </si>
-  <si>
-    <t>수완양우내안애 1차</t>
-  </si>
-  <si>
-    <t>수완 우미린2차</t>
-  </si>
-  <si>
-    <t>수완 영무예다음 2차</t>
-  </si>
-  <si>
-    <t>모아엘가 수완</t>
-  </si>
-  <si>
-    <t>성덕마을 대방노블랜드 5차</t>
-  </si>
-  <si>
-    <t>수완대주피오레</t>
-  </si>
-  <si>
-    <t>신가주공</t>
-  </si>
-  <si>
-    <t>수완2차중흥</t>
-  </si>
-  <si>
-    <t>수완휴먼시아 4단지</t>
-  </si>
-  <si>
-    <t>수완휴먼시아 6단지</t>
-  </si>
-  <si>
-    <t>진흥더루벤스</t>
-  </si>
-  <si>
-    <t>수완휴먼시아 1단지</t>
-  </si>
-  <si>
-    <t>아름마을휴먼시아 2단지</t>
-  </si>
-  <si>
-    <t>수완1차 중흥</t>
-  </si>
-  <si>
-    <t>수완 대방노블랜드</t>
-  </si>
-  <si>
-    <t>수완 대방3차</t>
-  </si>
-  <si>
-    <t>수완 호반베르디움 2차</t>
-  </si>
-  <si>
-    <t>수완골드클래스2차</t>
-  </si>
-  <si>
-    <t>수완영무예다음</t>
-  </si>
-  <si>
-    <t>수완문화체육센터(체육진흥과-지상)</t>
-  </si>
-  <si>
-    <t>수완문화체육센터(교통지도과-지하/체육과-지상)</t>
-  </si>
-  <si>
-    <t>광주 명진고등학교</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로 261</t>
-  </si>
-  <si>
-    <t>광주 광산구 장신로 85</t>
-  </si>
-  <si>
-    <t>광주 광산구 장신로 120</t>
-  </si>
-  <si>
-    <t>광주 광산구 수완로 6</t>
-  </si>
-  <si>
-    <t>광주 광산구 장신로50번길 20-3</t>
-  </si>
-  <si>
-    <t>광주 광산구 수완로 160</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로 330</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로 331</t>
-  </si>
-  <si>
-    <t>광주 광산구 장신로 77</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로 348</t>
-  </si>
-  <si>
-    <t>광주 광산구 임방울대로 342</t>
-  </si>
-  <si>
-    <t>광주 광산구 왕버들로 220</t>
-  </si>
-  <si>
-    <t>광주 광산구 장신로 52</t>
-  </si>
-  <si>
-    <t>광주 광산구 수완로 130</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로 300</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로 125</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로 65</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로 11</t>
-  </si>
-  <si>
-    <t>광주 광산구 수완로105번길 47</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로229번길 30</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로 45</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로 75</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로 155</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로94번길 31</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로170번길 39-9</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로95번길 45</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로 205</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로137번길 39</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로330번길 34</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로145번길 42</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로101번길 22</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로330번길 16</t>
-  </si>
-  <si>
-    <t>광주 광산구 왕버들로132번길 22</t>
-  </si>
-  <si>
-    <t>광주 광산구 수완로33번길 79</t>
-  </si>
-  <si>
-    <t>광주 광산구 목련로381번길 27</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로170번길 39-26</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로170번길 39-25</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로 204</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로145번길 15</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로145번길 43</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로329번길 51</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로6번길 35</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로123번길 70</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로123번길 22</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로76번길 74</t>
-  </si>
-  <si>
-    <t>광주 광산구 수등로76번길 40</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로170번길 39-10</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로329번길 19</t>
-  </si>
-  <si>
-    <t>광주 광산구 풍영로 285</t>
-  </si>
-  <si>
-    <t>광주 광산구 장덕로95번길 15</t>
-  </si>
-  <si>
-    <t>광주 광산구 왕버들로132번길 11</t>
-  </si>
-  <si>
-    <t>광주 광산구 수완로12번길 21</t>
-  </si>
-  <si>
-    <t>정은진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8대 (급속1대) (완속7대), 1대 (급속), 10대 (급속)</t>
-  </si>
-  <si>
-    <t>2대 C02 (지하1층), 2대 C03, 5대 D02</t>
-  </si>
-  <si>
-    <t>2층 (전용1/충전1) 비상구앞</t>
-  </si>
-  <si>
-    <t>1층 1대</t>
-  </si>
-  <si>
-    <t>1층 주차장 (전용4/충전4)</t>
-  </si>
-  <si>
-    <t>지하1층 2대</t>
-  </si>
-  <si>
-    <t>지상 입구앞 (2대)</t>
-  </si>
-  <si>
-    <t>주차장입구 1대</t>
-  </si>
-  <si>
-    <t>지상 주차장입구 1대</t>
-  </si>
-  <si>
-    <t>교문입구 1대</t>
-  </si>
-  <si>
-    <t>지상 (안내옆) 1대</t>
-  </si>
-  <si>
-    <t>운동장옆 지상 1대</t>
-  </si>
-  <si>
-    <t>교문옆 1대</t>
-  </si>
-  <si>
-    <t>지상1대 연못뒤</t>
-  </si>
-  <si>
-    <t>교문앞 1대</t>
-  </si>
-  <si>
-    <t>교문입구 바로옆 1대</t>
-  </si>
-  <si>
-    <t>지상 (전용 5 충전 5) 102동앞, 지상 (전용 3 충전 3) 105동앞, 지상 (전용 5 충전 5) 103동앞</t>
-  </si>
-  <si>
-    <t>지상 (전용 6 충전 6) 105동 앞, 지상 (전용 3 충전 3) 104동 앞</t>
-  </si>
-  <si>
-    <t>지하1층 (전용7 충전1) C18구역, 지하1층 (전용2 충전2) A4구역, 지하1층 (전용2 충전2) A8구역, 지하1층 (전용2 충전2) B17구역, 지하1층 (전용2 충전2) A6구역, 지하1층 (전용2 충전2) B19구역, 지하1층 (전용2 충전2) A5구역, 지하2층 (전용4 충전4) 병행4 H19구역, 지하2층 (전용3 충전3) 병행3 H4구역</t>
-  </si>
-  <si>
-    <t>지상(전용3 충전3) 201동앞, 지상(전용3 충전3) 202동앞 (병행3)</t>
-  </si>
-  <si>
-    <t>지하1층 108~109동 사이: 전용2/충전2, 지하2층 A23: 전용3/충전3, 지하2층 A80: 전용1/충전1, 지하2층 A40: 전용4/충전4, 지하2층 A29: 전용9/충전9, 지하2층 A38: 전용2/충전2, 지하2층 A39: 전용4/충전4</t>
-  </si>
-  <si>
-    <t>104동 2대 (C10) 지하, 106동 2대 (D20) 지하, 102동 1대 (A19) 지하, 105동 5대 지상, 110동 5대 지상</t>
-  </si>
-  <si>
-    <t>지하3동 : 전용3/충전3, 502동앞 : 전용3, 502동앞(분리수거장옆) : 전용 6/충전3, 503동앞 : 전용4</t>
-  </si>
-  <si>
-    <t>지상 (전용2 충전2) 105동 1문앞, 지상 (전용3 충전3) 103동 1문앞, 지상 (전용3 충전3) 정문 좌측, 지상 (전용4 충전4) 정문 우측</t>
-  </si>
-  <si>
-    <t>지하1층 (겸용 5 충전 5) A01구역, 지상 (전용 3 충전 3) 103동 앞, 지상 (전용 3 충전 3) 102동 앞</t>
-  </si>
-  <si>
-    <t>지상 (전용 3 충전 3) 211동앞, 지상 (전용 3 충전 3) 211동앞, 지상 (전용 3 충전 3) 208동앞, 지상 (전용 3 충전 3) 208동앞, 지상 (전용 3 충전 3) 201동앞, 지상 (전용 3 충전 3) 205동앞, 지하 (전용 3 충전 3) 25구역 (겸용 3), 지하 (전용 3 충전 3) 혼용 1, 지하 (3) 197구역, 지하 (3) R62 (병행 3)</t>
-  </si>
-  <si>
-    <t>지하1층 (전용 5 충전 5) 병행 4대 F구역, 지하1층 (전용 2 충전 2) 병행 1대 H구역, 지하1층 (전용 3 충전 3) A구역</t>
-  </si>
-  <si>
-    <t xml:space="preserve">① 지하(전용 1 충전 1) B42구역, ② 지하(전용 1 충전 1) R22구역, ③ 지하(전용 1 충전 1) 107동 입구 R37구역, ④ 지하(전용 1 충전 1) Y72구역, 지하(전용 1 충전 1) Y56구역, ⑤ 지하(전용 1 충전 1) R54구역, ⑥ 지상(전용 4 충전 4) 104동앞, ⑦ 지상(전용 4 충전 4) 104동앞, ⑧ 지상(전용 1 충전 1) 아파트입구 </t>
-  </si>
-  <si>
-    <t>지상 (겸용 2 충전 2) 504동 뒤, 지하 2층 (전용 15 충전 15) 겸용 3 17구역 겸용 2 (30구역), 지하 2층 (전용 3 충전3) 42구역</t>
-  </si>
-  <si>
-    <t>관리동앞 4대, 103동앞 3대, 104동앞 3대, 102동앞 2대(병행)</t>
-  </si>
-  <si>
-    <t>104동 앞 : 전용18/충전7</t>
-  </si>
-  <si>
-    <t>지하 (전용3 충전3) 병행 2 B23, 지하 (전용2 충전2) A19, 지하 (전용 4 충전4) 병행3 A68, 지하 (전용2 충전2) A71</t>
-  </si>
-  <si>
-    <t>406동앞 : 전용7/충전7, 402동앞 : 전용2/충전2, 403동앞 : 전용2/충전2</t>
-  </si>
-  <si>
-    <t>602동 6개, 610동 9개, 지하 601동 1개, 603동 1개(C4), 607동 1개(B1), 608동 1개(A3), 604동 1개(A4)</t>
-  </si>
-  <si>
-    <t>지하 (전용 6 충전 6) 병행 6, 지상 (전용 5 충전 5) 106동앞, 지상 (전용 10 충전 10) 급속 1 106동앞 (병행 2), 지상 (전용 1 충전1) 106동뒤</t>
-  </si>
-  <si>
-    <t>101동 앞 : 전용3/충전 1, 1지하주차장 : 전용3/충전 3, 2지하주차장 : 전용7/충전 7, 106동 후면 : 전용 2, 107동 후면 : 전용 2, 105동 후면 : 전용 2, 108동 후면 : 전용 3, 102동 후면 : 전용 2, 104동 측면 : 전용 3</t>
-  </si>
-  <si>
-    <t>213동 앞 : 전용 8/충전 8, 3지하주차장 : 전용 4/충전 4, 2지하주차장 : 전용 3/충전 3, 1지하주차장 : 전용 3/충전 3</t>
-  </si>
-  <si>
-    <t>관리동 옆 지하 전용3/충전3, 111동 후면 지하 전용2/충전2, 109동 옆 지하 전용2/충전2, 112동 옆 지하 전용3/충전3</t>
-  </si>
-  <si>
-    <t>108동 앞 전용3/충전3, 105동 앞 전용3/충전3, 103동 앞 전용6/충전6, 103동 후면 : 전용2/충전2, 102동 앞 : 전용1/충전1, 101동 앞 : 전용3/충전3</t>
-  </si>
-  <si>
-    <t>301동 3대, 306동 2대, 303동 3개</t>
-  </si>
-  <si>
-    <t>203동 1대, 206동 1대, 209동 1대</t>
-  </si>
-  <si>
-    <t>204동 지하2대, 210동 4대 (지상)</t>
-  </si>
-  <si>
-    <t>102동앞: 지상 전용5/충전5, 지하 101동: 전용2/충전2, 지하 102동: 전용2/충전2</t>
-  </si>
-  <si>
-    <t>지하1층 (전용1 충전1)급속1, 지하1층 (전용3) &lt;교통지도과&gt;, 지상 (전용3) &lt;체육진흥과&gt;</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1032,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1371,6 +1042,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1402,17 +1079,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1788,7 +1496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N149"/>
+  <dimension ref="A1:N154"/>
   <sheetFormatPr defaultRowHeight="11.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.69140625" style="2" customWidth="1"/>
@@ -1810,44 +1518,44 @@
   <sheetData>
     <row r="1" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>181</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>184</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>185</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>186</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>187</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>182</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
@@ -1855,15 +1563,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>234</v>
+        <v>110</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1872,24 +1580,22 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1898,24 +1604,22 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="1" t="s">
-        <v>5</v>
-      </c>
+      <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>236</v>
+        <v>112</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1924,24 +1628,22 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1" t="s">
-        <v>7</v>
-      </c>
+      <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>237</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1950,24 +1652,22 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>238</v>
+        <v>114</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1976,24 +1676,22 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -2002,24 +1700,22 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>240</v>
+        <v>116</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -2028,24 +1724,22 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>241</v>
+        <v>117</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -2054,24 +1748,22 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>242</v>
+        <v>118</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -2080,24 +1772,22 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>243</v>
+        <v>119</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -2106,24 +1796,22 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -2132,24 +1820,22 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>245</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -2158,24 +1844,22 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>246</v>
+        <v>122</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -2184,24 +1868,22 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>247</v>
+        <v>123</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -2210,24 +1892,22 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>248</v>
+        <v>124</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -2236,24 +1916,22 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="N16" s="1"/>
     </row>
     <row r="17" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>249</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -2262,24 +1940,22 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="N17" s="1"/>
     </row>
     <row r="18" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>250</v>
+        <v>126</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -2288,24 +1964,22 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="N18" s="1"/>
     </row>
     <row r="19" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>251</v>
+        <v>127</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -2314,24 +1988,22 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="N19" s="1"/>
     </row>
     <row r="20" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>252</v>
+        <v>128</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -2340,24 +2012,22 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="N20" s="1"/>
     </row>
     <row r="21" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>253</v>
+        <v>129</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -2366,24 +2036,22 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="N21" s="1"/>
     </row>
     <row r="22" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>254</v>
+        <v>130</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -2392,24 +2060,22 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="N22" s="1"/>
     </row>
     <row r="23" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>255</v>
+        <v>131</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -2418,24 +2084,22 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -2444,24 +2108,22 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="N24" s="1"/>
     </row>
     <row r="25" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -2477,15 +2139,15 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>258</v>
+        <v>134</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -2494,24 +2156,22 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="N26" s="1"/>
     </row>
     <row r="27" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>259</v>
+        <v>135</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2520,24 +2180,22 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27" s="1" t="s">
-        <v>52</v>
-      </c>
+      <c r="N27" s="1"/>
     </row>
     <row r="28" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>260</v>
+        <v>136</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2546,24 +2204,22 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28" s="1" t="s">
-        <v>54</v>
-      </c>
+      <c r="N28" s="1"/>
     </row>
     <row r="29" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>261</v>
+        <v>137</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -2572,24 +2228,22 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="N29" s="1"/>
     </row>
     <row r="30" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>262</v>
+        <v>138</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2598,24 +2252,22 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="N30" s="1"/>
     </row>
     <row r="31" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2624,24 +2276,22 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="N31" s="1"/>
     </row>
     <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2650,24 +2300,22 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="N32" s="1"/>
     </row>
     <row r="33" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>265</v>
+        <v>141</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2676,24 +2324,22 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="1" t="s">
-        <v>64</v>
-      </c>
+      <c r="N33" s="1"/>
     </row>
     <row r="34" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>266</v>
+        <v>142</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2702,24 +2348,22 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="N34" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2728,24 +2372,22 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="N35" s="1"/>
     </row>
     <row r="36" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>268</v>
+        <v>144</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2754,24 +2396,22 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="N36" s="1" t="s">
-        <v>70</v>
-      </c>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>269</v>
+        <v>145</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2787,15 +2427,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>270</v>
+        <v>146</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -2804,24 +2444,22 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-      <c r="N38" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2830,24 +2468,22 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
-      <c r="N39" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>272</v>
+        <v>148</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2856,24 +2492,22 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
-      <c r="N40" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>273</v>
+        <v>149</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2882,24 +2516,22 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
-      <c r="N41" s="1" t="s">
-        <v>79</v>
-      </c>
+      <c r="N41" s="1"/>
     </row>
     <row r="42" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>274</v>
+        <v>150</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2908,24 +2540,22 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-      <c r="N42" s="1" t="s">
-        <v>81</v>
-      </c>
+      <c r="N42" s="1"/>
     </row>
     <row r="43" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -2934,24 +2564,22 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-      <c r="N43" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>276</v>
+        <v>152</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2960,24 +2588,22 @@
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-      <c r="N44" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="N44" s="1"/>
     </row>
     <row r="45" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>277</v>
+        <v>153</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2986,24 +2612,22 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="N45" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -3018,16 +2642,16 @@
       <c r="A47" s="1">
         <v>46</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>89</v>
+      <c r="B47" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>179</v>
+        <v>108</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -3036,24 +2660,22 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="N47" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -3062,24 +2684,22 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
-      <c r="N48" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>93</v>
+        <v>157</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -3088,24 +2708,22 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="N49" s="1" t="s">
-        <v>94</v>
-      </c>
+      <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -3114,24 +2732,22 @@
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
-      <c r="N50" s="1" t="s">
-        <v>96</v>
-      </c>
+      <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -3140,24 +2756,22 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
-      <c r="N51" s="1" t="s">
-        <v>98</v>
-      </c>
+      <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -3166,24 +2780,22 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
-      <c r="N52" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -3192,24 +2804,22 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
-      <c r="N53" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -3218,24 +2828,22 @@
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
-      <c r="N54" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -3244,24 +2852,22 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
-      <c r="N55" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -3270,24 +2876,22 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
-      <c r="N56" s="1" t="s">
-        <v>279</v>
-      </c>
+      <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -3296,24 +2900,22 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
-      <c r="N57" s="1" t="s">
-        <v>110</v>
-      </c>
+      <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -3322,24 +2924,22 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
-      <c r="N58" s="1" t="s">
-        <v>112</v>
-      </c>
+      <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -3348,24 +2948,22 @@
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
-      <c r="N59" s="1" t="s">
-        <v>114</v>
-      </c>
+      <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -3374,24 +2972,22 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
-      <c r="N60" s="1" t="s">
-        <v>116</v>
-      </c>
+      <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -3407,15 +3003,15 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -3431,15 +3027,15 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -3455,15 +3051,15 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -3472,24 +3068,22 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
-      <c r="N64" s="1" t="s">
-        <v>123</v>
-      </c>
+      <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -3498,24 +3092,22 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
-      <c r="N65" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -3531,15 +3123,15 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -3548,24 +3140,22 @@
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="N67" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -3581,15 +3171,15 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -3598,24 +3188,22 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
-      <c r="N69" s="1" t="s">
-        <v>131</v>
-      </c>
+      <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -3624,24 +3212,22 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
-      <c r="N70" s="1" t="s">
-        <v>133</v>
-      </c>
+      <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -3650,24 +3236,22 @@
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
-      <c r="N71" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -3683,15 +3267,15 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -3700,24 +3284,22 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
-      <c r="N73" s="1" t="s">
-        <v>138</v>
-      </c>
+      <c r="N73" s="1"/>
     </row>
     <row r="74" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -3733,15 +3315,15 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -3757,15 +3339,15 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -3774,24 +3356,22 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
-      <c r="N76" s="1" t="s">
-        <v>142</v>
-      </c>
+      <c r="N76" s="1"/>
     </row>
     <row r="77" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>143</v>
+        <v>185</v>
       </c>
       <c r="C77" s="1"/>
-      <c r="D77" s="3" t="s">
-        <v>218</v>
+      <c r="D77" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -3800,24 +3380,22 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
-      <c r="N77" s="1" t="s">
-        <v>144</v>
-      </c>
+      <c r="N77" s="1"/>
     </row>
     <row r="78" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="C78" s="1"/>
-      <c r="D78" s="3" t="s">
-        <v>218</v>
+      <c r="D78" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -3826,24 +3404,22 @@
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
-      <c r="N78" s="1" t="s">
-        <v>104</v>
-      </c>
+      <c r="N78" s="1"/>
     </row>
     <row r="79" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -3852,24 +3428,22 @@
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
-      <c r="N79" s="1" t="s">
-        <v>146</v>
-      </c>
+      <c r="N79" s="1"/>
     </row>
     <row r="80" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -3878,24 +3452,22 @@
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
-      <c r="N80" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="N80" s="1"/>
     </row>
     <row r="81" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -3904,24 +3476,22 @@
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
-      <c r="N81" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="N81" s="1"/>
     </row>
     <row r="82" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -3930,24 +3500,22 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
-      <c r="N82" s="1" t="s">
-        <v>152</v>
-      </c>
+      <c r="N82" s="1"/>
     </row>
     <row r="83" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -3956,24 +3524,22 @@
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
-      <c r="N83" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="N83" s="1"/>
     </row>
     <row r="84" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -3982,24 +3548,22 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
-      <c r="N84" s="1" t="s">
-        <v>156</v>
-      </c>
+      <c r="N84" s="1"/>
     </row>
     <row r="85" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -4008,24 +3572,22 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
-      <c r="N85" s="1" t="s">
-        <v>158</v>
-      </c>
+      <c r="N85" s="1"/>
     </row>
     <row r="86" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -4034,24 +3596,22 @@
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
-      <c r="N86" s="1" t="s">
-        <v>160</v>
-      </c>
+      <c r="N86" s="1"/>
     </row>
     <row r="87" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C87" s="1"/>
-      <c r="D87" s="3" t="s">
-        <v>227</v>
+      <c r="D87" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -4060,24 +3620,22 @@
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
-      <c r="N87" s="1" t="s">
-        <v>162</v>
-      </c>
+      <c r="N87" s="1"/>
     </row>
     <row r="88" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1"/>
-      <c r="D88" s="3" t="s">
-        <v>227</v>
+      <c r="D88" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -4086,24 +3644,22 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
-      <c r="N88" s="1" t="s">
-        <v>121</v>
-      </c>
+      <c r="N88" s="1"/>
     </row>
     <row r="89" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -4112,24 +3668,22 @@
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
       <c r="M89" s="1"/>
-      <c r="N89" s="1" t="s">
-        <v>164</v>
-      </c>
+      <c r="N89" s="1"/>
     </row>
     <row r="90" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -4138,24 +3692,22 @@
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
       <c r="M90" s="1"/>
-      <c r="N90" s="1" t="s">
-        <v>166</v>
-      </c>
+      <c r="N90" s="1"/>
     </row>
     <row r="91" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -4164,24 +3716,22 @@
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
       <c r="M91" s="1"/>
-      <c r="N91" s="1" t="s">
-        <v>168</v>
-      </c>
+      <c r="N91" s="1"/>
     </row>
     <row r="92" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -4190,24 +3740,22 @@
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
       <c r="M92" s="1"/>
-      <c r="N92" s="1" t="s">
-        <v>170</v>
-      </c>
+      <c r="N92" s="1"/>
     </row>
     <row r="93" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -4216,24 +3764,22 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
-      <c r="N93" s="1" t="s">
-        <v>172</v>
-      </c>
+      <c r="N93" s="1"/>
     </row>
     <row r="94" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -4242,24 +3788,22 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
-      <c r="N94" s="1" t="s">
-        <v>174</v>
-      </c>
+      <c r="N94" s="1"/>
     </row>
     <row r="95" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="1" t="s">
-        <v>333</v>
+        <v>285</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -4268,24 +3812,22 @@
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
-      <c r="N95" s="4" t="s">
-        <v>386</v>
-      </c>
+      <c r="N95" s="4"/>
     </row>
     <row r="96" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="1" t="s">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -4301,15 +3843,15 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="1" t="s">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -4325,15 +3867,15 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="1" t="s">
-        <v>336</v>
+        <v>288</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -4342,24 +3884,22 @@
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
-      <c r="N98" s="4" t="s">
-        <v>387</v>
-      </c>
+      <c r="N98" s="4"/>
     </row>
     <row r="99" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="1" t="s">
-        <v>337</v>
+        <v>289</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -4375,15 +3915,15 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="1" t="s">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -4392,24 +3932,22 @@
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
-      <c r="N100" s="4" t="s">
-        <v>388</v>
-      </c>
+      <c r="N100" s="4"/>
     </row>
     <row r="101" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="1" t="s">
-        <v>339</v>
+        <v>291</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -4425,15 +3963,15 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="1" t="s">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
@@ -4442,24 +3980,22 @@
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
-      <c r="N102" s="4" t="s">
-        <v>389</v>
-      </c>
+      <c r="N102" s="4"/>
     </row>
     <row r="103" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="1" t="s">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
@@ -4475,15 +4011,15 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="1" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -4499,15 +4035,15 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="1" t="s">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
@@ -4523,15 +4059,15 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="1" t="s">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
@@ -4540,24 +4076,22 @@
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
-      <c r="N106" s="4" t="s">
-        <v>390</v>
-      </c>
+      <c r="N106" s="4"/>
     </row>
     <row r="107" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="1" t="s">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
@@ -4566,24 +4100,22 @@
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
-      <c r="N107" s="4" t="s">
-        <v>391</v>
-      </c>
+      <c r="N107" s="4"/>
     </row>
     <row r="108" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="1" t="s">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
@@ -4592,24 +4124,22 @@
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
-      <c r="N108" s="4" t="s">
-        <v>392</v>
-      </c>
+      <c r="N108" s="4"/>
     </row>
     <row r="109" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="1" t="s">
-        <v>347</v>
+        <v>299</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
@@ -4618,24 +4148,22 @@
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
-      <c r="N109" s="4" t="s">
-        <v>393</v>
-      </c>
+      <c r="N109" s="4"/>
     </row>
     <row r="110" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="1" t="s">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -4644,24 +4172,22 @@
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
-      <c r="N110" s="4" t="s">
-        <v>394</v>
-      </c>
+      <c r="N110" s="4"/>
     </row>
     <row r="111" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="1" t="s">
-        <v>349</v>
+        <v>301</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
@@ -4670,24 +4196,22 @@
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
-      <c r="N111" s="4" t="s">
-        <v>395</v>
-      </c>
+      <c r="N111" s="4"/>
     </row>
     <row r="112" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>297</v>
+        <v>265</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="1" t="s">
-        <v>350</v>
+        <v>302</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
@@ -4696,24 +4220,22 @@
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
-      <c r="N112" s="4" t="s">
-        <v>396</v>
-      </c>
+      <c r="N112" s="4"/>
     </row>
     <row r="113" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="1" t="s">
-        <v>351</v>
+        <v>303</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
@@ -4722,24 +4244,22 @@
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
-      <c r="N113" s="4" t="s">
-        <v>397</v>
-      </c>
+      <c r="N113" s="4"/>
     </row>
     <row r="114" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="C114" s="4"/>
-      <c r="D114" s="1" t="s">
-        <v>352</v>
+      <c r="D114" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
@@ -4748,24 +4268,22 @@
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
-      <c r="N114" s="4" t="s">
-        <v>398</v>
-      </c>
+      <c r="N114" s="4"/>
     </row>
     <row r="115" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="C115" s="4"/>
-      <c r="D115" s="1" t="s">
-        <v>353</v>
+      <c r="D115" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
@@ -4774,24 +4292,22 @@
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
-      <c r="N115" s="4" t="s">
-        <v>399</v>
-      </c>
+      <c r="N115" s="4"/>
     </row>
     <row r="116" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="1" t="s">
-        <v>354</v>
+        <v>305</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
@@ -4800,24 +4316,22 @@
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
-      <c r="N116" s="4" t="s">
-        <v>400</v>
-      </c>
+      <c r="N116" s="4"/>
     </row>
     <row r="117" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="1" t="s">
-        <v>355</v>
+        <v>306</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
@@ -4826,24 +4340,22 @@
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
-      <c r="N117" s="4" t="s">
-        <v>401</v>
-      </c>
+      <c r="N117" s="4"/>
     </row>
     <row r="118" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="1" t="s">
-        <v>356</v>
+        <v>307</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
@@ -4852,24 +4364,22 @@
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
-      <c r="N118" s="4" t="s">
-        <v>402</v>
-      </c>
+      <c r="N118" s="4"/>
     </row>
     <row r="119" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="1" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -4878,24 +4388,22 @@
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
-      <c r="N119" s="4" t="s">
-        <v>403</v>
-      </c>
+      <c r="N119" s="4"/>
     </row>
     <row r="120" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="1" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -4904,24 +4412,22 @@
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
-      <c r="N120" s="4" t="s">
-        <v>404</v>
-      </c>
+      <c r="N120" s="4"/>
     </row>
     <row r="121" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="1" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -4930,24 +4436,22 @@
       <c r="K121" s="4"/>
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
-      <c r="N121" s="4" t="s">
-        <v>405</v>
-      </c>
+      <c r="N121" s="4"/>
     </row>
     <row r="122" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="1" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -4956,24 +4460,22 @@
       <c r="K122" s="4"/>
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
-      <c r="N122" s="4" t="s">
-        <v>406</v>
-      </c>
+      <c r="N122" s="4"/>
     </row>
     <row r="123" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="1" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -4982,24 +4484,22 @@
       <c r="K123" s="4"/>
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
-      <c r="N123" s="4" t="s">
-        <v>407</v>
-      </c>
+      <c r="N123" s="4"/>
     </row>
     <row r="124" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="1" t="s">
-        <v>362</v>
+        <v>313</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -5008,24 +4508,22 @@
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
-      <c r="N124" s="4" t="s">
-        <v>408</v>
-      </c>
+      <c r="N124" s="4"/>
     </row>
     <row r="125" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="1" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -5034,24 +4532,22 @@
       <c r="K125" s="4"/>
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
-      <c r="N125" s="4" t="s">
-        <v>409</v>
-      </c>
+      <c r="N125" s="4"/>
     </row>
     <row r="126" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="1" t="s">
-        <v>364</v>
+        <v>315</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -5060,24 +4556,22 @@
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
-      <c r="N126" s="4" t="s">
-        <v>410</v>
-      </c>
+      <c r="N126" s="4"/>
     </row>
     <row r="127" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="1" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
@@ -5086,24 +4580,22 @@
       <c r="K127" s="4"/>
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
-      <c r="N127" s="4" t="s">
-        <v>411</v>
-      </c>
+      <c r="N127" s="4"/>
     </row>
     <row r="128" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="1" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
@@ -5112,24 +4604,22 @@
       <c r="K128" s="4"/>
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
-      <c r="N128" s="4" t="s">
-        <v>412</v>
-      </c>
+      <c r="N128" s="4"/>
     </row>
     <row r="129" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="1" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
@@ -5138,24 +4628,22 @@
       <c r="K129" s="4"/>
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
-      <c r="N129" s="4" t="s">
-        <v>413</v>
-      </c>
+      <c r="N129" s="4"/>
     </row>
     <row r="130" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>129</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>315</v>
+      <c r="B130" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C130" s="4"/>
       <c r="D130" s="1" t="s">
-        <v>368</v>
+        <v>37</v>
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
@@ -5164,24 +4652,22 @@
       <c r="K130" s="4"/>
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
-      <c r="N130" s="4" t="s">
-        <v>414</v>
-      </c>
+      <c r="N130" s="4"/>
     </row>
     <row r="131" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>130</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>316</v>
+      <c r="B131" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C131" s="4"/>
       <c r="D131" s="1" t="s">
-        <v>369</v>
+        <v>38</v>
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -5190,24 +4676,22 @@
       <c r="K131" s="4"/>
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
-      <c r="N131" s="4" t="s">
-        <v>415</v>
-      </c>
+      <c r="N131" s="4"/>
     </row>
     <row r="132" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>131</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>317</v>
+      <c r="B132" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C132" s="4"/>
       <c r="D132" s="1" t="s">
-        <v>370</v>
+        <v>40</v>
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -5216,24 +4700,22 @@
       <c r="K132" s="4"/>
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
-      <c r="N132" s="4" t="s">
-        <v>416</v>
-      </c>
+      <c r="N132" s="4"/>
     </row>
     <row r="133" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>132</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>318</v>
+      <c r="B133" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C133" s="4"/>
       <c r="D133" s="1" t="s">
-        <v>371</v>
+        <v>41</v>
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -5242,24 +4724,22 @@
       <c r="K133" s="4"/>
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
-      <c r="N133" s="4" t="s">
-        <v>417</v>
-      </c>
+      <c r="N133" s="4"/>
     </row>
     <row r="134" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>133</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>319</v>
+      <c r="B134" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="1" t="s">
-        <v>372</v>
+        <v>43</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
@@ -5268,24 +4748,22 @@
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
-      <c r="N134" s="4" t="s">
-        <v>418</v>
-      </c>
+      <c r="N134" s="4"/>
     </row>
     <row r="135" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>134</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>320</v>
+      <c r="B135" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="1" t="s">
-        <v>373</v>
+        <v>44</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
@@ -5294,24 +4772,22 @@
       <c r="K135" s="4"/>
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
-      <c r="N135" s="4" t="s">
-        <v>419</v>
-      </c>
+      <c r="N135" s="4"/>
     </row>
     <row r="136" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>135</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>321</v>
+      <c r="B136" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="1" t="s">
-        <v>374</v>
+        <v>45</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
@@ -5320,24 +4796,22 @@
       <c r="K136" s="4"/>
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
-      <c r="N136" s="4" t="s">
-        <v>420</v>
-      </c>
+      <c r="N136" s="4"/>
     </row>
     <row r="137" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>136</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>322</v>
+      <c r="B137" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C137" s="4"/>
       <c r="D137" s="1" t="s">
-        <v>375</v>
+        <v>46</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
@@ -5346,24 +4820,22 @@
       <c r="K137" s="4"/>
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
-      <c r="N137" s="4" t="s">
-        <v>421</v>
-      </c>
+      <c r="N137" s="4"/>
     </row>
     <row r="138" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>137</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>323</v>
+      <c r="B138" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="1" t="s">
-        <v>376</v>
+        <v>47</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
@@ -5372,24 +4844,22 @@
       <c r="K138" s="4"/>
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
-      <c r="N138" s="4" t="s">
-        <v>422</v>
-      </c>
+      <c r="N138" s="4"/>
     </row>
     <row r="139" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>138</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>324</v>
+      <c r="B139" s="5" t="s">
+        <v>319</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="1" t="s">
-        <v>377</v>
+        <v>48</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
@@ -5398,24 +4868,22 @@
       <c r="K139" s="4"/>
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
-      <c r="N139" s="4" t="s">
-        <v>423</v>
-      </c>
+      <c r="N139" s="4"/>
     </row>
     <row r="140" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>139</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>325</v>
+      <c r="B140" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="1" t="s">
-        <v>378</v>
+        <v>49</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
@@ -5424,24 +4892,22 @@
       <c r="K140" s="4"/>
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
-      <c r="N140" s="4" t="s">
-        <v>424</v>
-      </c>
+      <c r="N140" s="4"/>
     </row>
     <row r="141" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>140</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>326</v>
+      <c r="B141" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="C141" s="4"/>
       <c r="D141" s="1" t="s">
-        <v>379</v>
+        <v>50</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
@@ -5450,24 +4916,22 @@
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
-      <c r="N141" s="4" t="s">
-        <v>425</v>
-      </c>
+      <c r="N141" s="4"/>
     </row>
     <row r="142" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>141</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>327</v>
+      <c r="B142" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="C142" s="4"/>
       <c r="D142" s="1" t="s">
-        <v>380</v>
+        <v>51</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
@@ -5476,24 +4940,22 @@
       <c r="K142" s="4"/>
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
-      <c r="N142" s="4" t="s">
-        <v>426</v>
-      </c>
+      <c r="N142" s="4"/>
     </row>
     <row r="143" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>142</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>328</v>
+      <c r="B143" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="1" t="s">
-        <v>381</v>
+        <v>52</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
@@ -5502,24 +4964,22 @@
       <c r="K143" s="4"/>
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
-      <c r="N143" s="4" t="s">
-        <v>427</v>
-      </c>
+      <c r="N143" s="4"/>
     </row>
     <row r="144" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>143</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>329</v>
+      <c r="B144" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="1" t="s">
-        <v>382</v>
+        <v>53</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
@@ -5528,24 +4988,22 @@
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
-      <c r="N144" s="4" t="s">
-        <v>428</v>
-      </c>
+      <c r="N144" s="4"/>
     </row>
     <row r="145" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>144</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>330</v>
+      <c r="B145" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="1" t="s">
-        <v>383</v>
+        <v>54</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
@@ -5560,16 +5018,16 @@
       <c r="A146" s="1">
         <v>145</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>331</v>
+      <c r="B146" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="1" t="s">
-        <v>383</v>
+        <v>55</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -5578,24 +5036,22 @@
       <c r="K146" s="4"/>
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
-      <c r="N146" s="4" t="s">
-        <v>429</v>
-      </c>
+      <c r="N146" s="4"/>
     </row>
     <row r="147" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>146</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>332</v>
+      <c r="B147" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="1" t="s">
-        <v>384</v>
+        <v>56</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="4" t="s">
-        <v>385</v>
+        <v>61</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
@@ -5606,22 +5062,195 @@
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
     </row>
-    <row r="148" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="1">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C148" s="4"/>
+      <c r="D148" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E148" s="4"/>
+      <c r="F148" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+      <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
+      <c r="K148" s="4"/>
+      <c r="L148" s="4"/>
+      <c r="M148" s="4"/>
+      <c r="N148" s="4"/>
+    </row>
+    <row r="149" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="1">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
+      <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
+      <c r="K149" s="4"/>
+      <c r="L149" s="4"/>
+      <c r="M149" s="4"/>
+      <c r="N149" s="4"/>
+    </row>
+    <row r="150" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="1">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C150" s="4"/>
+      <c r="D150" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E150" s="4"/>
+      <c r="F150" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+      <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
+      <c r="K150" s="4"/>
+      <c r="L150" s="4"/>
+      <c r="M150" s="4"/>
+      <c r="N150" s="4"/>
+    </row>
+    <row r="151" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="1">
+        <v>150</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C151" s="4"/>
+      <c r="D151" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+      <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
+      <c r="K151" s="4"/>
+      <c r="L151" s="4"/>
+      <c r="M151" s="4"/>
+      <c r="N151" s="4"/>
+    </row>
+    <row r="152" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="1">
+        <v>151</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="4"/>
+      <c r="D152" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E152" s="4"/>
+      <c r="F152" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+      <c r="I152" s="4"/>
+      <c r="J152" s="4"/>
+      <c r="K152" s="4"/>
+      <c r="L152" s="4"/>
+      <c r="M152" s="4"/>
+      <c r="N152" s="4"/>
+    </row>
+    <row r="153" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E153" s="4"/>
+      <c r="F153" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
+      <c r="K153" s="4"/>
+      <c r="L153" s="4"/>
+      <c r="M153" s="4"/>
+      <c r="N153" s="4"/>
+    </row>
+    <row r="154" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C154" s="4"/>
+      <c r="D154" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E154" s="4"/>
+      <c r="F154" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+      <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
+      <c r="K154" s="4"/>
+      <c r="L154" s="4"/>
+      <c r="M154" s="4"/>
+      <c r="N154" s="4"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D79:D87 D47:D77 D89:D94">
+  <conditionalFormatting sqref="D79:D87 D48:D77 D89:D94">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D78">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D95:D129">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D78">
+  <conditionalFormatting sqref="D2:D47">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D46">
+  <conditionalFormatting sqref="D130:D151">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D95:D147">
+  <conditionalFormatting sqref="D152:D154">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
 </worksheet>
 </file>
--- a/조사1.xlsx
+++ b/조사1.xlsx
@@ -159,9 +159,6 @@
     <t>광주 광산구 왕버들로 220</t>
   </si>
   <si>
-    <t>광주 광산구 수완로 130</t>
-  </si>
-  <si>
     <t>광주 광산구 장덕로95번길 45</t>
   </si>
   <si>
@@ -994,6 +991,10 @@
   </si>
   <si>
     <t>수완양우내안애 1차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광주 광산구 수완동 1149</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1090,17 +1091,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1563,15 +1554,15 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1587,15 +1578,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1611,15 +1602,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1635,15 +1626,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1659,15 +1650,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1683,15 +1674,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1707,15 +1698,15 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1731,15 +1722,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
@@ -1755,15 +1746,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1779,15 +1770,15 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1803,15 +1794,15 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1827,15 +1818,15 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1851,15 +1842,15 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1875,15 +1866,15 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1899,15 +1890,15 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1923,15 +1914,15 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1947,15 +1938,15 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1971,15 +1962,15 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1995,15 +1986,15 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -2019,15 +2010,15 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -2043,15 +2034,15 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -2067,15 +2058,15 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -2091,15 +2082,15 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -2115,15 +2106,15 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -2139,15 +2130,15 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -2163,15 +2154,15 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2187,15 +2178,15 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2211,15 +2202,15 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -2235,15 +2226,15 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2259,15 +2250,15 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2283,15 +2274,15 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2307,15 +2298,15 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2331,15 +2322,15 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -2355,15 +2346,15 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2379,15 +2370,15 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2403,15 +2394,15 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2427,15 +2418,15 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -2451,15 +2442,15 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2475,15 +2466,15 @@
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2499,15 +2490,15 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2523,15 +2514,15 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2547,15 +2538,15 @@
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
@@ -2571,15 +2562,15 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2595,15 +2586,15 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -2619,15 +2610,15 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
@@ -2643,15 +2634,15 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
@@ -2667,15 +2658,15 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
@@ -2691,15 +2682,15 @@
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
@@ -2715,15 +2706,15 @@
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -2739,15 +2730,15 @@
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -2763,15 +2754,15 @@
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -2787,15 +2778,15 @@
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
@@ -2811,15 +2802,15 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
@@ -2835,15 +2826,15 @@
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
@@ -2859,15 +2850,15 @@
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
@@ -2883,15 +2874,15 @@
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -2907,15 +2898,15 @@
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -2931,15 +2922,15 @@
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
@@ -2955,15 +2946,15 @@
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
@@ -2979,15 +2970,15 @@
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
@@ -3003,15 +2994,15 @@
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
@@ -3027,15 +3018,15 @@
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
@@ -3051,15 +3042,15 @@
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -3075,15 +3066,15 @@
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -3099,15 +3090,15 @@
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -3123,15 +3114,15 @@
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -3147,15 +3138,15 @@
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1"/>
@@ -3171,15 +3162,15 @@
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -3195,15 +3186,15 @@
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -3219,15 +3210,15 @@
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -3243,15 +3234,15 @@
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
@@ -3267,15 +3258,15 @@
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -3291,15 +3282,15 @@
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -3315,15 +3306,15 @@
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
@@ -3339,15 +3330,15 @@
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
@@ -3363,15 +3354,15 @@
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
@@ -3387,15 +3378,15 @@
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -3411,15 +3402,15 @@
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -3435,15 +3426,15 @@
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
@@ -3459,15 +3450,15 @@
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -3483,15 +3474,15 @@
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -3507,15 +3498,15 @@
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -3531,15 +3522,15 @@
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -3555,15 +3546,15 @@
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -3579,15 +3570,15 @@
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
@@ -3603,15 +3594,15 @@
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
@@ -3627,15 +3618,15 @@
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -3651,15 +3642,15 @@
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G89" s="1"/>
       <c r="H89" s="1"/>
@@ -3675,15 +3666,15 @@
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G90" s="1"/>
       <c r="H90" s="1"/>
@@ -3699,15 +3690,15 @@
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -3723,15 +3714,15 @@
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G92" s="1"/>
       <c r="H92" s="1"/>
@@ -3747,15 +3738,15 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -3771,15 +3762,15 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -3795,15 +3786,15 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G95" s="4"/>
       <c r="H95" s="4"/>
@@ -3819,15 +3810,15 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G96" s="4"/>
       <c r="H96" s="4"/>
@@ -3843,15 +3834,15 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G97" s="4"/>
       <c r="H97" s="4"/>
@@ -3867,15 +3858,15 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G98" s="4"/>
       <c r="H98" s="4"/>
@@ -3891,15 +3882,15 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G99" s="4"/>
       <c r="H99" s="4"/>
@@ -3915,15 +3906,15 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G100" s="4"/>
       <c r="H100" s="4"/>
@@ -3939,15 +3930,15 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G101" s="4"/>
       <c r="H101" s="4"/>
@@ -3963,15 +3954,15 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E102" s="4"/>
       <c r="F102" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="4"/>
@@ -3987,15 +3978,15 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E103" s="4"/>
       <c r="F103" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G103" s="4"/>
       <c r="H103" s="4"/>
@@ -4011,15 +4002,15 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E104" s="4"/>
       <c r="F104" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
@@ -4035,15 +4026,15 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E105" s="4"/>
       <c r="F105" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
@@ -4059,15 +4050,15 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E106" s="4"/>
       <c r="F106" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G106" s="4"/>
       <c r="H106" s="4"/>
@@ -4083,15 +4074,15 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E107" s="4"/>
       <c r="F107" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G107" s="4"/>
       <c r="H107" s="4"/>
@@ -4107,15 +4098,15 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E108" s="4"/>
       <c r="F108" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G108" s="4"/>
       <c r="H108" s="4"/>
@@ -4131,15 +4122,15 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E109" s="4"/>
       <c r="F109" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G109" s="4"/>
       <c r="H109" s="4"/>
@@ -4155,15 +4146,15 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E110" s="4"/>
       <c r="F110" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G110" s="4"/>
       <c r="H110" s="4"/>
@@ -4179,15 +4170,15 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E111" s="4"/>
       <c r="F111" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G111" s="4"/>
       <c r="H111" s="4"/>
@@ -4203,15 +4194,15 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E112" s="4"/>
       <c r="F112" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G112" s="4"/>
       <c r="H112" s="4"/>
@@ -4227,15 +4218,15 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E113" s="4"/>
       <c r="F113" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="4"/>
@@ -4251,15 +4242,15 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E114" s="4"/>
       <c r="F114" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="4"/>
@@ -4275,15 +4266,15 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C115" s="4"/>
       <c r="D115" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E115" s="4"/>
       <c r="F115" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
@@ -4299,15 +4290,15 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E116" s="4"/>
       <c r="F116" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G116" s="4"/>
       <c r="H116" s="4"/>
@@ -4323,15 +4314,15 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C117" s="4"/>
       <c r="D117" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E117" s="4"/>
       <c r="F117" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G117" s="4"/>
       <c r="H117" s="4"/>
@@ -4347,15 +4338,15 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C118" s="4"/>
       <c r="D118" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E118" s="4"/>
       <c r="F118" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
@@ -4371,15 +4362,15 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C119" s="4"/>
       <c r="D119" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E119" s="4"/>
       <c r="F119" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -4395,15 +4386,15 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C120" s="4"/>
       <c r="D120" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E120" s="4"/>
       <c r="F120" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
@@ -4419,15 +4410,15 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C121" s="4"/>
       <c r="D121" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E121" s="4"/>
       <c r="F121" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
@@ -4443,15 +4434,15 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E122" s="4"/>
       <c r="F122" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
@@ -4467,15 +4458,15 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C123" s="4"/>
       <c r="D123" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
@@ -4491,15 +4482,15 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C124" s="4"/>
       <c r="D124" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E124" s="4"/>
       <c r="F124" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
@@ -4515,15 +4506,15 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E125" s="4"/>
       <c r="F125" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
@@ -4539,15 +4530,15 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C126" s="4"/>
       <c r="D126" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
@@ -4563,15 +4554,15 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C127" s="4"/>
       <c r="D127" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E127" s="4"/>
       <c r="F127" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
@@ -4587,15 +4578,15 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E128" s="4"/>
       <c r="F128" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G128" s="4"/>
       <c r="H128" s="4"/>
@@ -4611,15 +4602,15 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E129" s="4"/>
       <c r="F129" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G129" s="4"/>
       <c r="H129" s="4"/>
@@ -4643,7 +4634,7 @@
       </c>
       <c r="E130" s="4"/>
       <c r="F130" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4"/>
@@ -4667,7 +4658,7 @@
       </c>
       <c r="E131" s="4"/>
       <c r="F131" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G131" s="4"/>
       <c r="H131" s="4"/>
@@ -4691,7 +4682,7 @@
       </c>
       <c r="E132" s="4"/>
       <c r="F132" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G132" s="4"/>
       <c r="H132" s="4"/>
@@ -4715,7 +4706,7 @@
       </c>
       <c r="E133" s="4"/>
       <c r="F133" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G133" s="4"/>
       <c r="H133" s="4"/>
@@ -4735,11 +4726,11 @@
       </c>
       <c r="C134" s="4"/>
       <c r="D134" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E134" s="4"/>
       <c r="F134" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G134" s="4"/>
       <c r="H134" s="4"/>
@@ -4759,11 +4750,11 @@
       </c>
       <c r="C135" s="4"/>
       <c r="D135" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E135" s="4"/>
       <c r="F135" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G135" s="4"/>
       <c r="H135" s="4"/>
@@ -4783,11 +4774,11 @@
       </c>
       <c r="C136" s="4"/>
       <c r="D136" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E136" s="4"/>
       <c r="F136" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
@@ -4807,11 +4798,11 @@
       </c>
       <c r="C137" s="4"/>
       <c r="D137" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E137" s="4"/>
       <c r="F137" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G137" s="4"/>
       <c r="H137" s="4"/>
@@ -4831,11 +4822,11 @@
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E138" s="4"/>
       <c r="F138" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G138" s="4"/>
       <c r="H138" s="4"/>
@@ -4851,15 +4842,15 @@
         <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C139" s="4"/>
       <c r="D139" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E139" s="4"/>
       <c r="F139" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G139" s="4"/>
       <c r="H139" s="4"/>
@@ -4879,11 +4870,11 @@
       </c>
       <c r="C140" s="4"/>
       <c r="D140" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E140" s="4"/>
       <c r="F140" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G140" s="4"/>
       <c r="H140" s="4"/>
@@ -4903,11 +4894,11 @@
       </c>
       <c r="C141" s="4"/>
       <c r="D141" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E141" s="4"/>
       <c r="F141" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="4"/>
@@ -4927,11 +4918,11 @@
       </c>
       <c r="C142" s="4"/>
       <c r="D142" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E142" s="4"/>
       <c r="F142" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G142" s="4"/>
       <c r="H142" s="4"/>
@@ -4951,11 +4942,11 @@
       </c>
       <c r="C143" s="4"/>
       <c r="D143" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E143" s="4"/>
       <c r="F143" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G143" s="4"/>
       <c r="H143" s="4"/>
@@ -4975,11 +4966,11 @@
       </c>
       <c r="C144" s="4"/>
       <c r="D144" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E144" s="4"/>
       <c r="F144" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G144" s="4"/>
       <c r="H144" s="4"/>
@@ -4999,11 +4990,11 @@
       </c>
       <c r="C145" s="4"/>
       <c r="D145" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E145" s="4"/>
       <c r="F145" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G145" s="4"/>
       <c r="H145" s="4"/>
@@ -5023,11 +5014,11 @@
       </c>
       <c r="C146" s="4"/>
       <c r="D146" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E146" s="4"/>
       <c r="F146" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G146" s="4"/>
       <c r="H146" s="4"/>
@@ -5047,11 +5038,11 @@
       </c>
       <c r="C147" s="4"/>
       <c r="D147" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E147" s="4"/>
       <c r="F147" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G147" s="4"/>
       <c r="H147" s="4"/>
@@ -5071,11 +5062,11 @@
       </c>
       <c r="C148" s="4"/>
       <c r="D148" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E148" s="4"/>
       <c r="F148" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="4"/>
@@ -5095,11 +5086,11 @@
       </c>
       <c r="C149" s="4"/>
       <c r="D149" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E149" s="4"/>
       <c r="F149" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G149" s="4"/>
       <c r="H149" s="4"/>
@@ -5119,11 +5110,11 @@
       </c>
       <c r="C150" s="4"/>
       <c r="D150" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E150" s="4"/>
       <c r="F150" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G150" s="4"/>
       <c r="H150" s="4"/>
@@ -5143,11 +5134,11 @@
       </c>
       <c r="C151" s="4"/>
       <c r="D151" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E151" s="4"/>
       <c r="F151" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
@@ -5171,7 +5162,7 @@
       </c>
       <c r="E152" s="4"/>
       <c r="F152" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
@@ -5191,11 +5182,11 @@
       </c>
       <c r="C153" s="4"/>
       <c r="D153" s="1" t="s">
-        <v>42</v>
+        <v>319</v>
       </c>
       <c r="E153" s="4"/>
       <c r="F153" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
@@ -5215,11 +5206,11 @@
       </c>
       <c r="C154" s="4"/>
       <c r="D154" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E154" s="4"/>
       <c r="F154" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
@@ -5233,10 +5224,10 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D79:D87 D48:D77 D89:D94">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D78">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D95:D129">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
